--- a/data/Tuning/FISC inyear extract QMFM EvM-AK Oct28.xlsx
+++ b/data/Tuning/FISC inyear extract QMFM EvM-AK Oct28.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75AD3097-B8C0-4332-B3E0-16C37A284CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30BD3734-8273-42F7-9643-E1B85A2984CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{D61D5969-636A-4DAC-AE1D-E00E6EDBBDA0}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" activeTab="1" xr2:uid="{D61D5969-636A-4DAC-AE1D-E00E6EDBBDA0}"/>
   </bookViews>
   <sheets>
     <sheet name="FiscTuning_Rw" sheetId="2" r:id="rId1"/>
@@ -23,6 +23,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -126,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="80">
   <si>
     <t>Extract from FISCAL in-year, with corrected GDP numbers, lonked to intMF FY GDP</t>
   </si>
@@ -402,6 +413,9 @@
     <t>Exchange rate RWF/USD (end of period) CY</t>
   </si>
   <si>
+    <t>Depr rate</t>
+  </si>
+  <si>
     <t>period average ER</t>
   </si>
   <si>
@@ -427,12 +441,6 @@
       </rPr>
       <t>allocate over semesters as govt equity</t>
     </r>
-  </si>
-  <si>
-    <t>Depr rate, %</t>
-  </si>
-  <si>
-    <t>Total equity (Bugesera+Qatar</t>
   </si>
 </sst>
 </file>
@@ -1249,7 +1257,6 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="170" fontId="26" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1261,6 +1268,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -6997,7 +7005,7 @@
     </row>
     <row r="67" spans="1:53" x14ac:dyDescent="0.75">
       <c r="A67" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AI67" s="94" t="s">
         <v>60</v>
@@ -7076,7 +7084,7 @@
     </row>
     <row r="68" spans="1:53" x14ac:dyDescent="0.75">
       <c r="A68" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI68" s="79"/>
       <c r="AJ68" s="96">
@@ -7167,11 +7175,11 @@
         <f t="shared" ref="AK69:AZ69" si="26">+(AK67+AK68)/AK27</f>
         <v>3.5550430472671372E-3</v>
       </c>
-      <c r="AL69" s="117">
+      <c r="AL69" s="116">
         <f t="shared" si="26"/>
         <v>3.7277171331734922E-2</v>
       </c>
-      <c r="AM69" s="117">
+      <c r="AM69" s="116">
         <f t="shared" si="26"/>
         <v>5.4785913549554137E-2</v>
       </c>
@@ -7179,11 +7187,11 @@
         <f t="shared" si="26"/>
         <v>4.6031542440644529E-2</v>
       </c>
-      <c r="AO69" s="117">
+      <c r="AO69" s="116">
         <f t="shared" si="26"/>
         <v>3.3923685167178079E-2</v>
       </c>
-      <c r="AP69" s="117">
+      <c r="AP69" s="116">
         <f t="shared" si="26"/>
         <v>3.9198390972127059E-2</v>
       </c>
@@ -7191,11 +7199,11 @@
         <f t="shared" si="26"/>
         <v>3.6561038069652572E-2</v>
       </c>
-      <c r="AR69" s="117">
+      <c r="AR69" s="116">
         <f t="shared" si="26"/>
         <v>3.3391888487969368E-2</v>
       </c>
-      <c r="AS69" s="117">
+      <c r="AS69" s="116">
         <f t="shared" si="26"/>
         <v>1.8962175027440388E-2</v>
       </c>
@@ -7203,11 +7211,11 @@
         <f t="shared" si="26"/>
         <v>2.6177031757704878E-2</v>
       </c>
-      <c r="AU69" s="117">
+      <c r="AU69" s="116">
         <f t="shared" si="26"/>
         <v>2.4223295422375626E-3</v>
       </c>
-      <c r="AV69" s="117">
+      <c r="AV69" s="116">
         <f t="shared" si="26"/>
         <v>2.4282105743104322E-3</v>
       </c>
@@ -7215,11 +7223,11 @@
         <f t="shared" si="26"/>
         <v>2.4252700582739974E-3</v>
       </c>
-      <c r="AX69" s="117">
+      <c r="AX69" s="116">
         <f t="shared" si="26"/>
         <v>1.9440881185176268E-3</v>
       </c>
-      <c r="AY69" s="117">
+      <c r="AY69" s="116">
         <f t="shared" si="26"/>
         <v>2.0424927645828427E-3</v>
       </c>
@@ -7234,7 +7242,7 @@
         <v>Jul-Dec</v>
       </c>
       <c r="AM71" s="44" t="str">
-        <f t="shared" ref="AM71:AS71" si="27">+AM36</f>
+        <f t="shared" ref="AM71:AQ71" si="27">+AM36</f>
         <v>Jan-Jun</v>
       </c>
       <c r="AN71" s="43" t="str">
@@ -7253,18 +7261,7 @@
         <f t="shared" si="27"/>
         <v>2026/2027</v>
       </c>
-      <c r="AR71" s="44" t="str">
-        <f t="shared" si="27"/>
-        <v>Jul-Dec</v>
-      </c>
-      <c r="AS71" s="44" t="str">
-        <f t="shared" si="27"/>
-        <v>Jan-Jun</v>
-      </c>
-      <c r="AT71" s="43" t="str">
-        <f t="shared" ref="AT71" si="28">+AT36</f>
-        <v>2027/2028</v>
-      </c>
+      <c r="AR71" s="44"/>
     </row>
     <row r="72" spans="1:53" x14ac:dyDescent="0.75">
       <c r="AJ72" s="90" t="s">
@@ -7280,39 +7277,39 @@
         <v>4.1296290255148554E-2</v>
       </c>
       <c r="AL73" s="47">
-        <f t="shared" ref="AL73:AM73" si="29">+AL57</f>
+        <f t="shared" ref="AL73:AM73" si="28">+AL57</f>
         <v>3.7277171331734922E-2</v>
       </c>
       <c r="AM73" s="47">
+        <f t="shared" si="28"/>
+        <v>5.4785913549554137E-2</v>
+      </c>
+      <c r="AN73" s="82">
+        <f t="shared" ref="AN73:AT73" si="29">+AN57</f>
+        <v>4.6031542440644529E-2</v>
+      </c>
+      <c r="AO73" s="47">
         <f t="shared" si="29"/>
-        <v>5.4785913549554137E-2</v>
-      </c>
-      <c r="AN73" s="82">
-        <f t="shared" ref="AN73:AT73" si="30">+AN57</f>
-        <v>4.6031542440644529E-2</v>
-      </c>
-      <c r="AO73" s="47">
-        <f t="shared" si="30"/>
         <v>3.3923685167178079E-2</v>
       </c>
       <c r="AP73" s="47">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>3.9198390972127059E-2</v>
       </c>
       <c r="AQ73" s="82">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>3.6561038069652572E-2</v>
       </c>
       <c r="AR73" s="47">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>3.3391888487969368E-2</v>
       </c>
       <c r="AS73" s="47">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1.8962175027440388E-2</v>
       </c>
       <c r="AT73" s="82">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>2.6177031757704878E-2</v>
       </c>
       <c r="AU73" s="47"/>
@@ -7388,7 +7385,7 @@
         <v>0.13593362208986398</v>
       </c>
       <c r="AR75" s="86">
-        <f t="shared" ref="AR75" si="31">+$AT$73/$AJ$75*$AJ$78*AR78</f>
+        <f t="shared" ref="AR75" si="30">+$AT$73/$AJ$75*$AJ$78*AR78</f>
         <v>8.7256772525682924E-2</v>
       </c>
       <c r="AS75" s="86">
@@ -7406,7 +7403,7 @@
       <c r="AN76" s="103"/>
     </row>
     <row r="77" spans="1:53" x14ac:dyDescent="0.75">
-      <c r="AJ77" s="118" t="s">
+      <c r="AJ77" s="117" t="s">
         <v>58</v>
       </c>
       <c r="AK77" s="45" t="s">
@@ -7434,7 +7431,7 @@
       </c>
     </row>
     <row r="78" spans="1:53" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="AJ78" s="119">
+      <c r="AJ78" s="118">
         <v>0.5</v>
       </c>
       <c r="AL78" s="88">
@@ -7600,7 +7597,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C7" s="110">
         <f>C6/B6-1</f>
@@ -7629,7 +7626,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B8" s="107"/>
       <c r="C8" s="107">
@@ -7661,88 +7658,81 @@
       <c r="C9" s="110"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="115">
+      <c r="C10" s="114">
         <f>+C2*C8/1000</f>
         <v>438.27158639249711</v>
       </c>
-      <c r="D10" s="115">
+      <c r="D10" s="114">
         <f t="shared" ref="D10:G10" si="3">+D2*D8/1000</f>
         <v>1072.1962144377621</v>
       </c>
-      <c r="E10" s="115">
+      <c r="E10" s="114">
         <f t="shared" si="3"/>
         <v>1131.19496605123</v>
       </c>
-      <c r="F10" s="115">
+      <c r="F10" s="114">
         <f t="shared" si="3"/>
         <v>299.54417097422845</v>
       </c>
-      <c r="G10" s="115">
+      <c r="G10" s="114">
         <f t="shared" si="3"/>
         <v>6.9174693636110227</v>
       </c>
-      <c r="H10" s="114">
-        <f>SUM(C10:G10)</f>
-        <v>2948.1244072193285</v>
-      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A11" s="113" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" s="116">
+        <v>77</v>
+      </c>
+      <c r="C11" s="115">
         <f>+C3*C$8/1000</f>
         <v>246.91180946464326</v>
       </c>
-      <c r="D11" s="116">
+      <c r="D11" s="115">
         <f t="shared" ref="D11:G11" si="4">+D3*D$8/1000</f>
         <v>572.98423296231954</v>
       </c>
-      <c r="E11" s="116">
+      <c r="E11" s="115">
         <f t="shared" si="4"/>
         <v>678.71697963073848</v>
       </c>
-      <c r="F11" s="116">
+      <c r="F11" s="115">
         <f t="shared" si="4"/>
         <v>179.72650258453717</v>
       </c>
-      <c r="G11" s="116">
+      <c r="G11" s="115">
         <f t="shared" si="4"/>
         <v>4.150481618166614</v>
       </c>
-      <c r="H11" s="114">
+      <c r="H11" s="119">
         <f>SUM(C11:G11)</f>
         <v>1682.4900062604052</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A12" s="113" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="116">
+        <v>78</v>
+      </c>
+      <c r="C12" s="115">
         <f t="shared" ref="C12:G12" si="5">+C4*C$8/1000</f>
         <v>191.35977692785386</v>
       </c>
-      <c r="D12" s="116">
+      <c r="D12" s="115">
         <f t="shared" si="5"/>
         <v>499.21198147544249</v>
       </c>
-      <c r="E12" s="116">
+      <c r="E12" s="115">
         <f t="shared" si="5"/>
         <v>452.47798642049156</v>
       </c>
-      <c r="F12" s="116">
+      <c r="F12" s="115">
         <f t="shared" si="5"/>
         <v>119.81766838969132</v>
       </c>
-      <c r="G12" s="116">
+      <c r="G12" s="115">
         <f t="shared" si="5"/>
         <v>2.7669877454444092</v>
       </c>
-      <c r="H12" s="114">
+      <c r="H12" s="119">
         <f>SUM(C12:G12)</f>
         <v>1265.6344009589236</v>
       </c>

--- a/data/Tuning/FISC inyear extract QMFM EvM-AK Oct28.xlsx
+++ b/data/Tuning/FISC inyear extract QMFM EvM-AK Oct28.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\GitHub\QMFM\data\Tuning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30BD3734-8273-42F7-9643-E1B85A2984CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C213A17A-CAA4-4222-A84D-8DF6D4445F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" activeTab="1" xr2:uid="{D61D5969-636A-4DAC-AE1D-E00E6EDBBDA0}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{D61D5969-636A-4DAC-AE1D-E00E6EDBBDA0}"/>
   </bookViews>
   <sheets>
     <sheet name="FiscTuning_Rw" sheetId="2" r:id="rId1"/>
@@ -23,17 +23,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -7327,29 +7316,29 @@
       </c>
       <c r="AL74" s="83">
         <f>+$AJ$73/$AJ$75*$AJ$78*AL77</f>
-        <v>8.9475295552821868E-2</v>
+        <v>4.4737647776410934E-2</v>
       </c>
       <c r="AM74" s="84">
         <f>+$AJ$73/$AJ$75*$AJ$78*AM77</f>
-        <v>0.15830244597806944</v>
+        <v>7.9151222989034722E-2</v>
       </c>
       <c r="AN74" s="52"/>
       <c r="AO74" s="84">
         <f>+$AJ$73/$AJ$75*$AJ$78*AO77</f>
-        <v>0.17895059110564374</v>
+        <v>8.9475295552821868E-2</v>
       </c>
       <c r="AP74" s="84">
         <f>+$AJ$73/$AJ$75*$AJ$78*AP77</f>
-        <v>0.1170061557229209</v>
+        <v>5.8503077861460452E-2</v>
       </c>
       <c r="AQ74" s="102"/>
       <c r="AR74" s="84">
         <f>+$AT$73/$AJ$75*$AJ$78*AR77</f>
-        <v>8.7256772525682924E-2</v>
+        <v>4.3628386262841462E-2</v>
       </c>
       <c r="AS74" s="84">
         <f>+$AT$73/$AJ$75*$AJ$78*AS77</f>
-        <v>8.7256772525682924E-2</v>
+        <v>4.3628386262841462E-2</v>
       </c>
       <c r="AT74" s="55"/>
     </row>
@@ -7362,39 +7351,39 @@
       </c>
       <c r="AL75" s="85">
         <f>+$AJ$73/$AJ$75*$AJ$78*AL78</f>
-        <v>0.1170061557229209</v>
+        <v>5.8503077861460452E-2</v>
       </c>
       <c r="AM75" s="86">
         <f>+$AJ$73/$AJ$75*$AJ$78*AM78</f>
-        <v>0.17895059110564374</v>
+        <v>8.9475295552821868E-2</v>
       </c>
       <c r="AN75" s="60">
         <f>AVERAGE(AL74:AM76)</f>
-        <v>0.13593362208986398</v>
+        <v>6.7966811044931991E-2</v>
       </c>
       <c r="AO75" s="86">
         <f>+$AJ$73/$AJ$75*$AJ$78*AO78</f>
-        <v>0.15830244597806944</v>
+        <v>7.9151222989034722E-2</v>
       </c>
       <c r="AP75" s="86">
         <f>+$AJ$73/$AJ$75*$AJ$78*AP78</f>
-        <v>8.9475295552821868E-2</v>
+        <v>4.4737647776410934E-2</v>
       </c>
       <c r="AQ75" s="60">
         <f>AVERAGE(AO74:AP76)</f>
-        <v>0.13593362208986398</v>
+        <v>6.7966811044931991E-2</v>
       </c>
       <c r="AR75" s="86">
         <f t="shared" ref="AR75" si="30">+$AT$73/$AJ$75*$AJ$78*AR78</f>
-        <v>8.7256772525682924E-2</v>
+        <v>4.3628386262841462E-2</v>
       </c>
       <c r="AS75" s="86">
         <f>+$AT$73/$AJ$75*$AJ$78*AS78</f>
-        <v>8.7256772525682924E-2</v>
+        <v>4.3628386262841462E-2</v>
       </c>
       <c r="AT75" s="60">
         <f>AVERAGE(AR74:AS76)</f>
-        <v>8.7256772525682924E-2</v>
+        <v>4.3628386262841462E-2</v>
       </c>
     </row>
     <row r="76" spans="1:53" ht="16.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.9">
@@ -7432,7 +7421,7 @@
     </row>
     <row r="78" spans="1:53" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="AJ78" s="118">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AL78" s="88">
         <v>0.85</v>

--- a/data/Tuning/FISC inyear extract QMFM EvM-AK Oct28.xlsx
+++ b/data/Tuning/FISC inyear extract QMFM EvM-AK Oct28.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\GitHub\QMFM\data\Tuning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C213A17A-CAA4-4222-A84D-8DF6D4445F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EDC0ECC-C3D0-4966-9A6C-03FA54F57824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{D61D5969-636A-4DAC-AE1D-E00E6EDBBDA0}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D61D5969-636A-4DAC-AE1D-E00E6EDBBDA0}"/>
   </bookViews>
   <sheets>
     <sheet name="FiscTuning_Rw" sheetId="2" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="88">
   <si>
     <t>Extract from FISCAL in-year, with corrected GDP numbers, lonked to intMF FY GDP</t>
   </si>
@@ -431,6 +431,30 @@
       <t>allocate over semesters as govt equity</t>
     </r>
   </si>
+  <si>
+    <t>2020/21</t>
+  </si>
+  <si>
+    <t>2021/22</t>
+  </si>
+  <si>
+    <t>2022/23</t>
+  </si>
+  <si>
+    <t>2023/24</t>
+  </si>
+  <si>
+    <t>2024/25</t>
+  </si>
+  <si>
+    <t>Sem</t>
+  </si>
+  <si>
+    <t>Diff</t>
+  </si>
+  <si>
+    <t>Annual</t>
+  </si>
 </sst>
 </file>
 
@@ -447,7 +471,7 @@
     <numFmt numFmtId="169" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="40" x14ac:knownFonts="1">
+  <fonts count="46" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -627,13 +651,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="1"/>
@@ -737,6 +754,63 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Display"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Display"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFA20000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1091,7 +1165,7 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1175,27 +1249,23 @@
     <xf numFmtId="165" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="3" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1205,59 +1275,93 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="27" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="23" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="23" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="23" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="23" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="37" fontId="28" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="27" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="167" fontId="39" fillId="8" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="38" fillId="8" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="36" fillId="5" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="35" fillId="5" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="36" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="35" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="25" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="26" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="36" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="35" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="39" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="40" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="41" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="39" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="39" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="43" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="43" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="34" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="43" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="43" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="45" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="34" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="43" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="34" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="34" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="43" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1276,6 +1380,1315 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>FiscTuning_Rw!$A$83</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Grev in % of GDP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>FiscTuning_Rw!$AE$81:$AP$81</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>2018/19</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2019/20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2020/21</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2021/22</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2022/23</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023/24</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2024/25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2025/2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2026/2027</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2027/2028</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2028/2029</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2029/2030</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>FiscTuning_Rw!$AE$83:$AP$83</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.19014996739316092</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.18314644640250893</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.19117087620602016</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.18431901010679033</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.17014303403236622</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.16620417789665298</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.16546014323811886</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.17626652465618078</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.18383799968178346</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.18786735635011592</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.18985626615967205</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.19254613324113448</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-759E-49F2-9548-6D139F759BD5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>FiscTuning_Rw!$A$84</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Gdem in % of GDP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>FiscTuning_Rw!$AE$81:$AP$81</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>2018/19</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2019/20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2020/21</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2021/22</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2022/23</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023/24</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2024/25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2025/2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2026/2027</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2027/2028</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2028/2029</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2029/2030</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>FiscTuning_Rw!$AE$84:$AP$84</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.26169584838513593</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.26811145968691313</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.27570065921784898</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.28377582490937286</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.24368260292576732</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.22612197687473534</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.20053719230054018</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.19544292641226998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.19708559679766124</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.20500503475212281</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.20621080279034229</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.21126024180894573</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-759E-49F2-9548-6D139F759BD5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>FiscTuning_Rw!$A$88</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Tot Spending in % of GDP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>FiscTuning_Rw!$AE$81:$AP$81</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>2018/19</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2019/20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2020/21</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2021/22</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2022/23</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023/24</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2024/25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2025/2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2026/2027</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2027/2028</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2028/2029</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2029/2030</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>FiscTuning_Rw!$AE$88:$AP$88</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.27139661636466372</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.29958819734316722</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.32366045585195247</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.33670696675965084</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.35185267843523671</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.29533472921204673</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.27432440534114733</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.26074866732077423</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.25459257192894552</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.25394326992505989</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.24174570649612137</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.24333466449664484</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-759E-49F2-9548-6D139F759BD5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>FiscTuning_Rw!$A$89</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Deficit (Excl. Grants ) % of GDP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>FiscTuning_Rw!$AE$81:$AP$81</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>2018/19</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2019/20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2020/21</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2021/22</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2022/23</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023/24</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2024/25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2025/2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2026/2027</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2027/2028</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2028/2029</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2029/2030</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>FiscTuning_Rw!$AE$89:$AP$89</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>-0.10715311961052623</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.13198602648404975</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.13819197250543944</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.1569715400252282</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.11571481494483828</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.10810529497455036</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0.0%">
+                  <c:v>-8.3344978076517584E-2</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0.0%">
+                  <c:v>-8.4482142664593501E-2</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0.0%">
+                  <c:v>-7.0754572247162029E-2</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0.0%">
+                  <c:v>-6.6075913574943954E-2</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0.0%">
+                  <c:v>-5.1889440336449273E-2</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0.0%">
+                  <c:v>-5.0788531255510416E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-759E-49F2-9548-6D139F759BD5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1038695440"/>
+        <c:axId val="906329424"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1038695440"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-RW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="906329424"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="906329424"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-RW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1038695440"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-RW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-RW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>555624</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1DE0E61-1D67-11A6-3D25-7B76930AC5C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1598,16 +3011,27 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:BC79"/>
+  <dimension ref="A2:BC89"/>
   <sheetFormatPr defaultRowHeight="14.75" outlineLevelCol="1" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="43.26953125" customWidth="1"/>
     <col min="2" max="25" width="8.7265625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="26" max="26" width="10.6328125" hidden="1" customWidth="1" collapsed="1"/>
-    <col min="27" max="30" width="10.6328125" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="11.81640625" hidden="1" customWidth="1"/>
-    <col min="32" max="34" width="8.6328125" style="3" hidden="1" customWidth="1"/>
-    <col min="35" max="52" width="9.6328125" style="3" customWidth="1"/>
+    <col min="26" max="26" width="10.6328125" customWidth="1" collapsed="1"/>
+    <col min="27" max="30" width="10.6328125" customWidth="1"/>
+    <col min="31" max="31" width="11.81640625" customWidth="1"/>
+    <col min="32" max="34" width="8.6328125" style="3" customWidth="1"/>
+    <col min="35" max="36" width="9.6328125" style="3" customWidth="1"/>
+    <col min="37" max="37" width="9.6328125" style="112" customWidth="1"/>
+    <col min="38" max="39" width="9.6328125" style="3" customWidth="1"/>
+    <col min="40" max="40" width="9.6328125" style="112" customWidth="1"/>
+    <col min="41" max="42" width="9.6328125" style="3" customWidth="1"/>
+    <col min="43" max="43" width="9.6328125" style="112" customWidth="1"/>
+    <col min="44" max="45" width="9.6328125" style="3" customWidth="1"/>
+    <col min="46" max="46" width="9.6328125" style="112" customWidth="1"/>
+    <col min="47" max="48" width="9.6328125" style="3" customWidth="1"/>
+    <col min="49" max="49" width="9.6328125" style="112" customWidth="1"/>
+    <col min="50" max="51" width="9.6328125" style="3" customWidth="1"/>
+    <col min="52" max="52" width="9.6328125" style="112" customWidth="1"/>
     <col min="53" max="53" width="9.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1967,7 +3391,7 @@
       <c r="AH7" s="12"/>
       <c r="AI7" s="14"/>
       <c r="AJ7" s="14"/>
-      <c r="AK7" s="14">
+      <c r="AK7" s="113">
         <v>20033.689823079447</v>
       </c>
       <c r="AL7" s="14">
@@ -1976,7 +3400,7 @@
       <c r="AM7" s="14">
         <v>11326.738119159327</v>
       </c>
-      <c r="AN7" s="14">
+      <c r="AN7" s="113">
         <v>22653.476238318653</v>
       </c>
       <c r="AO7" s="14">
@@ -1985,7 +3409,7 @@
       <c r="AP7" s="14">
         <v>12781.239907852294</v>
       </c>
-      <c r="AQ7" s="14">
+      <c r="AQ7" s="113">
         <v>25562.479815704588</v>
       </c>
       <c r="AR7" s="14">
@@ -1994,7 +3418,7 @@
       <c r="AS7" s="14">
         <v>14387.536018309578</v>
       </c>
-      <c r="AT7" s="14">
+      <c r="AT7" s="113">
         <v>28775.072036619156</v>
       </c>
       <c r="AU7" s="14">
@@ -2003,7 +3427,7 @@
       <c r="AV7" s="14">
         <v>16166.704197489691</v>
       </c>
-      <c r="AW7" s="14">
+      <c r="AW7" s="113">
         <v>32333.408394979382</v>
       </c>
       <c r="AX7" s="14">
@@ -2012,7 +3436,7 @@
       <c r="AY7" s="14">
         <v>18163.761804602887</v>
       </c>
-      <c r="AZ7" s="14">
+      <c r="AZ7" s="113">
         <v>36327.523609205775</v>
       </c>
     </row>
@@ -2055,7 +3479,7 @@
       <c r="AH8" s="12"/>
       <c r="AI8" s="15"/>
       <c r="AJ8" s="15"/>
-      <c r="AK8" s="15">
+      <c r="AK8" s="114">
         <v>0.18265969901885684</v>
       </c>
       <c r="AL8" s="15">
@@ -2064,7 +3488,7 @@
       <c r="AM8" s="15">
         <v>0.19342862639163508</v>
       </c>
-      <c r="AN8" s="15">
+      <c r="AN8" s="114">
         <v>0.1877252152300235</v>
       </c>
       <c r="AO8" s="15">
@@ -2073,7 +3497,7 @@
       <c r="AP8" s="15">
         <v>0.20347286117005281</v>
       </c>
-      <c r="AQ8" s="15">
+      <c r="AQ8" s="114">
         <v>0.19739150930448318</v>
       </c>
       <c r="AR8" s="15">
@@ -2082,7 +3506,7 @@
       <c r="AS8" s="15">
         <v>0.20882982480919066</v>
       </c>
-      <c r="AT8" s="15">
+      <c r="AT8" s="114">
         <v>0.20261452250610237</v>
       </c>
       <c r="AU8" s="15">
@@ -2091,7 +3515,7 @@
       <c r="AV8" s="15">
         <v>0.21105666189556113</v>
       </c>
-      <c r="AW8" s="15">
+      <c r="AW8" s="114">
         <v>0.20477012399691286</v>
       </c>
       <c r="AX8" s="15">
@@ -2100,7 +3524,7 @@
       <c r="AY8" s="15">
         <v>0.21296624659299274</v>
       </c>
-      <c r="AZ8" s="15">
+      <c r="AZ8" s="114">
         <v>0.20661377678750092</v>
       </c>
     </row>
@@ -2143,7 +3567,7 @@
       <c r="AH9" s="12"/>
       <c r="AI9" s="15"/>
       <c r="AJ9" s="15"/>
-      <c r="AK9" s="15">
+      <c r="AK9" s="114">
         <v>0.21618191762249483</v>
       </c>
       <c r="AL9" s="15">
@@ -2152,7 +3576,7 @@
       <c r="AM9" s="15">
         <v>0.18220563884602761</v>
       </c>
-      <c r="AN9" s="15">
+      <c r="AN9" s="114">
         <v>0.20214246706919278</v>
       </c>
       <c r="AO9" s="15">
@@ -2161,7 +3585,7 @@
       <c r="AP9" s="15">
         <v>0.19146428712535027</v>
       </c>
-      <c r="AQ9" s="15">
+      <c r="AQ9" s="114">
         <v>0.2111616703583146</v>
       </c>
       <c r="AR9" s="15">
@@ -2170,7 +3594,7 @@
       <c r="AS9" s="15">
         <v>0.14106344180139738</v>
       </c>
-      <c r="AT9" s="15">
+      <c r="AT9" s="114">
         <v>0.21736809529944531</v>
       </c>
       <c r="AU9" s="15">
@@ -2179,7 +3603,7 @@
       <c r="AV9" s="15">
         <v>0.14565705261025019</v>
       </c>
-      <c r="AW9" s="15">
+      <c r="AW9" s="114">
         <v>0.21938605929611971</v>
       </c>
       <c r="AX9" s="15">
@@ -2188,7 +3612,7 @@
       <c r="AY9" s="15">
         <v>0.14627159152842076</v>
       </c>
-      <c r="AZ9" s="15">
+      <c r="AZ9" s="114">
         <v>0.21652717851044984</v>
       </c>
     </row>
@@ -2231,7 +3655,7 @@
       <c r="AH10" s="12"/>
       <c r="AI10" s="15"/>
       <c r="AJ10" s="15"/>
-      <c r="AK10" s="15">
+      <c r="AK10" s="114">
         <v>5.2313276029538544E-2</v>
       </c>
       <c r="AL10" s="15">
@@ -2240,7 +3664,7 @@
       <c r="AM10" s="15">
         <v>4.5857654055867912E-2</v>
       </c>
-      <c r="AN10" s="15">
+      <c r="AN10" s="114">
         <v>8.5188748614071663E-2</v>
       </c>
       <c r="AO10" s="15">
@@ -2249,7 +3673,7 @@
       <c r="AP10" s="15">
         <v>5.8352899484848814E-2</v>
       </c>
-      <c r="AQ10" s="15">
+      <c r="AQ10" s="114">
         <v>6.6546004576310824E-2</v>
       </c>
       <c r="AR10" s="15">
@@ -2258,7 +3682,7 @@
       <c r="AS10" s="15">
         <v>4.5252519773348869E-2</v>
       </c>
-      <c r="AT10" s="15">
+      <c r="AT10" s="114">
         <v>4.6622866372220864E-2</v>
       </c>
       <c r="AU10" s="15">
@@ -2267,7 +3691,7 @@
       <c r="AV10" s="15">
         <v>4.3614820920078026E-2</v>
       </c>
-      <c r="AW10" s="15">
+      <c r="AW10" s="114">
         <v>4.2409661748152208E-2</v>
       </c>
       <c r="AX10" s="15">
@@ -2276,7 +3700,7 @@
       <c r="AY10" s="15">
         <v>5.3553863939848227E-2</v>
       </c>
-      <c r="AZ10" s="15">
+      <c r="AZ10" s="114">
         <v>4.6238458036064918E-2</v>
       </c>
     </row>
@@ -2317,22 +3741,22 @@
       <c r="AH11" s="12"/>
       <c r="AI11" s="15"/>
       <c r="AJ11" s="15"/>
-      <c r="AK11" s="15"/>
+      <c r="AK11" s="114"/>
       <c r="AL11" s="15"/>
       <c r="AM11" s="15"/>
-      <c r="AN11" s="15"/>
+      <c r="AN11" s="114"/>
       <c r="AO11" s="15"/>
       <c r="AP11" s="15"/>
-      <c r="AQ11" s="15"/>
+      <c r="AQ11" s="114"/>
       <c r="AR11" s="15"/>
       <c r="AS11" s="15"/>
-      <c r="AT11" s="15"/>
+      <c r="AT11" s="114"/>
       <c r="AU11" s="15"/>
       <c r="AV11" s="15"/>
-      <c r="AW11" s="15"/>
+      <c r="AW11" s="114"/>
       <c r="AX11" s="15"/>
       <c r="AY11" s="15"/>
-      <c r="AZ11" s="15"/>
+      <c r="AZ11" s="114"/>
     </row>
     <row r="12" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A12" s="13"/>
@@ -2371,22 +3795,22 @@
       <c r="AH12" s="12"/>
       <c r="AI12" s="15"/>
       <c r="AJ12" s="15"/>
-      <c r="AK12" s="15"/>
+      <c r="AK12" s="114"/>
       <c r="AL12" s="15"/>
       <c r="AM12" s="15"/>
-      <c r="AN12" s="15"/>
+      <c r="AN12" s="114"/>
       <c r="AO12" s="15"/>
       <c r="AP12" s="15"/>
-      <c r="AQ12" s="15"/>
+      <c r="AQ12" s="114"/>
       <c r="AR12" s="15"/>
       <c r="AS12" s="15"/>
-      <c r="AT12" s="15"/>
+      <c r="AT12" s="114"/>
       <c r="AU12" s="15"/>
       <c r="AV12" s="15"/>
-      <c r="AW12" s="15"/>
+      <c r="AW12" s="114"/>
       <c r="AX12" s="15"/>
       <c r="AY12" s="15"/>
-      <c r="AZ12" s="15"/>
+      <c r="AZ12" s="114"/>
     </row>
     <row r="13" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A13" s="13" t="s">
@@ -2427,7 +3851,7 @@
       <c r="AH13" s="12"/>
       <c r="AI13" s="15"/>
       <c r="AJ13" s="15"/>
-      <c r="AK13" s="15">
+      <c r="AK13" s="114">
         <v>0.26849519365203339</v>
       </c>
       <c r="AL13" s="15">
@@ -2436,7 +3860,7 @@
       <c r="AM13" s="15">
         <v>0.22806329290189545</v>
       </c>
-      <c r="AN13" s="15">
+      <c r="AN13" s="114">
         <v>0.28733121568326442</v>
       </c>
       <c r="AO13" s="15">
@@ -2445,7 +3869,7 @@
       <c r="AP13" s="15">
         <v>0.24981998205640421</v>
       </c>
-      <c r="AQ13" s="15">
+      <c r="AQ13" s="114">
         <v>0.27770767493462539</v>
       </c>
       <c r="AR13" s="15">
@@ -2454,7 +3878,7 @@
       <c r="AS13" s="15">
         <v>8.1983015152663943E-2</v>
       </c>
-      <c r="AT13" s="15">
+      <c r="AT13" s="114">
         <v>0.26399096167166619</v>
       </c>
       <c r="AU13" s="15">
@@ -2463,7 +3887,7 @@
       <c r="AV13" s="15">
         <v>8.7007920333264793E-2</v>
       </c>
-      <c r="AW13" s="15">
+      <c r="AW13" s="114">
         <v>0.26179572104427185</v>
       </c>
       <c r="AX13" s="15">
@@ -2472,7 +3896,7 @@
       <c r="AY13" s="15">
         <v>8.6420688737840298E-2</v>
       </c>
-      <c r="AZ13" s="15">
+      <c r="AZ13" s="114">
         <v>0.2627656365465148</v>
       </c>
     </row>
@@ -2515,7 +3939,7 @@
       <c r="AH14" s="12"/>
       <c r="AI14" s="15"/>
       <c r="AJ14" s="15"/>
-      <c r="AK14" s="15">
+      <c r="AK14" s="114">
         <v>-8.5835494633176551E-2</v>
       </c>
       <c r="AL14" s="15">
@@ -2524,7 +3948,7 @@
       <c r="AM14" s="15">
         <v>-3.4634666510260363E-2</v>
       </c>
-      <c r="AN14" s="15">
+      <c r="AN14" s="114">
         <v>-9.9606000453240931E-2</v>
       </c>
       <c r="AO14" s="15">
@@ -2533,7 +3957,7 @@
       <c r="AP14" s="15">
         <v>-4.6347120886351449E-2</v>
       </c>
-      <c r="AQ14" s="15">
+      <c r="AQ14" s="114">
         <v>-8.0316165630142225E-2</v>
       </c>
       <c r="AR14" s="15">
@@ -2542,7 +3966,7 @@
       <c r="AS14" s="15">
         <v>-3.4941792018702664E-2</v>
       </c>
-      <c r="AT14" s="15">
+      <c r="AT14" s="114">
         <v>-6.1376439165563845E-2</v>
       </c>
       <c r="AU14" s="15">
@@ -2551,7 +3975,7 @@
       <c r="AV14" s="15">
         <v>-3.6269954070865654E-2</v>
       </c>
-      <c r="AW14" s="15">
+      <c r="AW14" s="114">
         <v>-5.7025597047359065E-2</v>
       </c>
       <c r="AX14" s="15">
@@ -2560,7 +3984,7 @@
       <c r="AY14" s="15">
         <v>-4.346487766586761E-2</v>
       </c>
-      <c r="AZ14" s="15">
+      <c r="AZ14" s="114">
         <v>-5.6151859759013864E-2</v>
       </c>
     </row>
@@ -2601,19 +4025,19 @@
       <c r="AH15" s="12"/>
       <c r="AI15" s="15"/>
       <c r="AJ15" s="15"/>
-      <c r="AK15" s="15"/>
+      <c r="AK15" s="114"/>
       <c r="AL15" s="15"/>
       <c r="AM15" s="15"/>
-      <c r="AN15" s="15"/>
+      <c r="AN15" s="114"/>
       <c r="AO15" s="15"/>
       <c r="AP15" s="15"/>
-      <c r="AQ15" s="15"/>
+      <c r="AQ15" s="114"/>
       <c r="AR15" s="15"/>
       <c r="AS15" s="15"/>
-      <c r="AT15" s="15"/>
+      <c r="AT15" s="114"/>
       <c r="AU15" s="15"/>
       <c r="AV15" s="15"/>
-      <c r="AW15" s="15"/>
+      <c r="AW15" s="114"/>
       <c r="AX15" s="12"/>
       <c r="AY15" s="12"/>
       <c r="AZ15" s="12"/>
@@ -2657,22 +4081,22 @@
       <c r="AH16" s="21"/>
       <c r="AI16" s="20"/>
       <c r="AJ16" s="20"/>
-      <c r="AK16" s="21"/>
+      <c r="AK16" s="136"/>
       <c r="AL16" s="22"/>
       <c r="AM16" s="22"/>
-      <c r="AN16" s="21"/>
+      <c r="AN16" s="136"/>
       <c r="AO16" s="22"/>
       <c r="AP16" s="22"/>
-      <c r="AQ16" s="21"/>
+      <c r="AQ16" s="136"/>
       <c r="AR16" s="22"/>
       <c r="AS16" s="22"/>
-      <c r="AT16" s="22"/>
+      <c r="AT16" s="115"/>
       <c r="AU16" s="22"/>
       <c r="AV16" s="22"/>
-      <c r="AW16" s="22"/>
+      <c r="AW16" s="115"/>
       <c r="AX16" s="22"/>
       <c r="AY16" s="22"/>
-      <c r="AZ16" s="22"/>
+      <c r="AZ16" s="115"/>
     </row>
     <row r="17" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A17" s="13" t="s">
@@ -2783,7 +4207,7 @@
       <c r="AJ17" s="25">
         <v>1776.112347501851</v>
       </c>
-      <c r="AK17" s="25">
+      <c r="AK17" s="116">
         <v>3559.3786013384124</v>
       </c>
       <c r="AL17" s="25">
@@ -2792,7 +4216,7 @@
       <c r="AM17" s="25">
         <v>2189.6457710714726</v>
       </c>
-      <c r="AN17" s="25">
+      <c r="AN17" s="116">
         <v>4303.2755565682201</v>
       </c>
       <c r="AO17" s="25">
@@ -2801,7 +4225,7 @@
       <c r="AP17" s="25">
         <v>2629.0879415666591</v>
       </c>
-      <c r="AQ17" s="25">
+      <c r="AQ17" s="116">
         <v>5090.8279828679388</v>
       </c>
       <c r="AR17" s="25">
@@ -2810,7 +4234,7 @@
       <c r="AS17" s="25">
         <v>3014.929216324671</v>
       </c>
-      <c r="AT17" s="25">
+      <c r="AT17" s="116">
         <v>5851.3838730814805</v>
       </c>
       <c r="AU17" s="25">
@@ -2819,7 +4243,7 @@
       <c r="AV17" s="25">
         <v>3415.513685793173</v>
       </c>
-      <c r="AW17" s="25">
+      <c r="AW17" s="116">
         <v>6628.6160838914857</v>
       </c>
       <c r="AX17" s="25">
@@ -2828,7 +4252,7 @@
       <c r="AY17" s="25">
         <v>3884.4148308322015</v>
       </c>
-      <c r="AZ17" s="25">
+      <c r="AZ17" s="116">
         <v>7539.082760930628</v>
       </c>
     </row>
@@ -2941,7 +4365,7 @@
       <c r="AJ18" s="25">
         <v>2089.1201441111698</v>
       </c>
-      <c r="AK18" s="25">
+      <c r="AK18" s="116">
         <v>4313.9560807692205</v>
       </c>
       <c r="AL18" s="25">
@@ -2950,7 +4374,7 @@
       <c r="AM18" s="25">
         <v>2352.8507458017857</v>
       </c>
-      <c r="AN18" s="25">
+      <c r="AN18" s="116">
         <v>4771.4378528458246</v>
       </c>
       <c r="AO18" s="25">
@@ -2959,7 +4383,7 @@
       <c r="AP18" s="25">
         <v>2447.765027387496</v>
       </c>
-      <c r="AQ18" s="25">
+      <c r="AQ18" s="116">
         <v>5457.6794402380656</v>
       </c>
       <c r="AR18" s="25">
@@ -2968,7 +4392,7 @@
       <c r="AS18" s="25">
         <v>2925.9658217176616</v>
       </c>
-      <c r="AT18" s="25">
+      <c r="AT18" s="116">
         <v>6385.160134012498</v>
       </c>
       <c r="AU18" s="25">
@@ -2977,7 +4401,7 @@
       <c r="AV18" s="25">
         <v>3355.5541731044013</v>
       </c>
-      <c r="AW18" s="25">
+      <c r="AW18" s="116">
         <v>7199.6161712074372</v>
       </c>
       <c r="AX18" s="25">
@@ -2986,7 +4410,7 @@
       <c r="AY18" s="25">
         <v>3872.967109043519</v>
       </c>
-      <c r="AZ18" s="25">
+      <c r="AZ18" s="116">
         <v>8271.8277447682412</v>
       </c>
     </row>
@@ -3099,7 +4523,7 @@
       <c r="AJ19" s="25">
         <v>508.8869360634871</v>
       </c>
-      <c r="AK19" s="25">
+      <c r="AK19" s="116">
         <v>1038.3396889512389</v>
       </c>
       <c r="AL19" s="25">
@@ -3108,7 +4532,7 @@
       <c r="AM19" s="25">
         <v>835.7217847964298</v>
       </c>
-      <c r="AN19" s="25">
+      <c r="AN19" s="116">
         <v>1594.339022133149</v>
       </c>
       <c r="AO19" s="25">
@@ -3117,7 +4541,7 @@
       <c r="AP19" s="25">
         <v>796.44888799147907</v>
       </c>
-      <c r="AQ19" s="25">
+      <c r="AQ19" s="116">
         <v>1592.4788058790109</v>
       </c>
       <c r="AR19" s="25">
@@ -3126,7 +4550,7 @@
       <c r="AS19" s="25">
         <v>696.39628771871696</v>
       </c>
-      <c r="AT19" s="25">
+      <c r="AT19" s="116">
         <v>1524.2477758314185</v>
       </c>
       <c r="AU19" s="25">
@@ -3135,7 +4559,7 @@
       <c r="AV19" s="25">
         <v>619.73834982054245</v>
       </c>
-      <c r="AW19" s="25">
+      <c r="AW19" s="116">
         <v>1240.660837844368</v>
       </c>
       <c r="AX19" s="25">
@@ -3144,7 +4568,7 @@
       <c r="AY19" s="25">
         <v>606.92732118801302</v>
       </c>
-      <c r="AZ19" s="25">
+      <c r="AZ19" s="116">
         <v>1255.8638445821318</v>
       </c>
     </row>
@@ -3209,7 +4633,7 @@
       <c r="AJ20" s="25">
         <v>52.640374271249001</v>
       </c>
-      <c r="AK20" s="25">
+      <c r="AK20" s="116">
         <v>163.95667452790599</v>
       </c>
       <c r="AL20" s="25">
@@ -3218,7 +4642,7 @@
       <c r="AM20" s="25">
         <v>346.67755839973131</v>
       </c>
-      <c r="AN20" s="25">
+      <c r="AN20" s="116">
         <v>592.32798369052716</v>
       </c>
       <c r="AO20" s="25">
@@ -3227,7 +4651,7 @@
       <c r="AP20" s="25">
         <v>272.80376678927291</v>
       </c>
-      <c r="AQ20" s="25">
+      <c r="AQ20" s="116">
         <v>511.08480257000514</v>
       </c>
       <c r="AR20" s="25">
@@ -3236,7 +4660,7 @@
       <c r="AS20" s="25">
         <v>154.60849343766787</v>
       </c>
-      <c r="AT20" s="25">
+      <c r="AT20" s="116">
         <v>415.44002998865113</v>
       </c>
       <c r="AU20" s="25">
@@ -3245,7 +4669,7 @@
       <c r="AV20" s="25">
         <v>35.65819267721988</v>
       </c>
-      <c r="AW20" s="25">
+      <c r="AW20" s="116">
         <v>70.066244679216851</v>
       </c>
       <c r="AX20" s="25">
@@ -3254,7 +4678,7 @@
       <c r="AY20" s="25">
         <v>33.925152397140423</v>
       </c>
-      <c r="AZ20" s="25">
+      <c r="AZ20" s="116">
         <v>65.783991693740418</v>
       </c>
     </row>
@@ -3319,7 +4743,7 @@
       <c r="AJ21" s="25">
         <v>27.199999999999996</v>
       </c>
-      <c r="AK21" s="25">
+      <c r="AK21" s="116">
         <v>36.150092620999999</v>
       </c>
       <c r="AL21" s="25">
@@ -3328,7 +4752,7 @@
       <c r="AM21" s="25">
         <v>316.12001089561022</v>
       </c>
-      <c r="AN21" s="25">
+      <c r="AN21" s="116">
         <v>531.21288868228487</v>
       </c>
       <c r="AO21" s="25">
@@ -3337,7 +4761,7 @@
       <c r="AP21" s="25">
         <v>256.55184526664607</v>
       </c>
-      <c r="AQ21" s="25">
+      <c r="AQ21" s="116">
         <v>478.58095952475151</v>
       </c>
       <c r="AR21" s="25">
@@ -3346,7 +4770,7 @@
       <c r="AS21" s="25">
         <v>139.58835294766789</v>
       </c>
-      <c r="AT21" s="25">
+      <c r="AT21" s="116">
         <v>385.39974900865116</v>
       </c>
       <c r="AU21" s="25">
@@ -3355,7 +4779,7 @@
       <c r="AV21" s="25">
         <v>20.037246567619881</v>
       </c>
-      <c r="AW21" s="25">
+      <c r="AW21" s="116">
         <v>40.025963699216845</v>
       </c>
       <c r="AX21" s="25">
@@ -3364,7 +4788,7 @@
       <c r="AY21" s="25">
         <v>18.901575342420418</v>
       </c>
-      <c r="AZ21" s="25">
+      <c r="AZ21" s="116">
         <v>36.892497357740417</v>
       </c>
     </row>
@@ -3477,7 +4901,7 @@
       <c r="AJ22" s="25">
         <v>2598.0070801746569</v>
       </c>
-      <c r="AK22" s="25">
+      <c r="AK22" s="116">
         <v>5352.2957697204592</v>
       </c>
       <c r="AL22" s="25">
@@ -3486,7 +4910,7 @@
       <c r="AM22" s="25">
         <v>3188.5725305982151</v>
       </c>
-      <c r="AN22" s="25">
+      <c r="AN22" s="116">
         <v>6365.776874978972</v>
       </c>
       <c r="AO22" s="25">
@@ -3495,7 +4919,7 @@
       <c r="AP22" s="25">
         <v>3244.2496446475725</v>
       </c>
-      <c r="AQ22" s="25">
+      <c r="AQ22" s="116">
         <v>7050.1582461170765</v>
       </c>
       <c r="AR22" s="25">
@@ -3504,7 +4928,7 @@
       <c r="AS22" s="25">
         <v>3622.3361948132733</v>
       </c>
-      <c r="AT22" s="25">
+      <c r="AT22" s="116">
         <v>7909.4079098439179</v>
       </c>
       <c r="AU22" s="25">
@@ -3513,7 +4937,7 @@
       <c r="AV22" s="25">
         <v>3975.3030129863655</v>
       </c>
-      <c r="AW22" s="25">
+      <c r="AW22" s="116">
         <v>8440.2770090518061</v>
       </c>
       <c r="AX22" s="25">
@@ -3522,7 +4946,7 @@
       <c r="AY22" s="25">
         <v>4479.9760440088176</v>
       </c>
-      <c r="AZ22" s="25">
+      <c r="AZ22" s="116">
         <v>9527.6915893503738</v>
       </c>
     </row>
@@ -3635,7 +5059,7 @@
       <c r="AJ23" s="25">
         <v>-821.89473267280573</v>
       </c>
-      <c r="AK23" s="25">
+      <c r="AK23" s="116">
         <v>-1792.9171683820464</v>
       </c>
       <c r="AL23" s="25">
@@ -3644,7 +5068,7 @@
       <c r="AM23" s="25">
         <v>-998.92675952674222</v>
       </c>
-      <c r="AN23" s="25">
+      <c r="AN23" s="116">
         <v>-2062.5013184107529</v>
       </c>
       <c r="AO23" s="25">
@@ -3653,7 +5077,7 @@
       <c r="AP23" s="25">
         <v>-615.16170308091318</v>
       </c>
-      <c r="AQ23" s="25">
+      <c r="AQ23" s="116">
         <v>-1959.3302632491377</v>
       </c>
       <c r="AR23" s="25">
@@ -3662,7 +5086,7 @@
       <c r="AS23" s="25">
         <v>-607.40697848860191</v>
       </c>
-      <c r="AT23" s="25">
+      <c r="AT23" s="116">
         <v>-2058.0240367624365</v>
       </c>
       <c r="AU23" s="25">
@@ -3671,7 +5095,7 @@
       <c r="AV23" s="25">
         <v>-559.78932719319278</v>
       </c>
-      <c r="AW23" s="25">
+      <c r="AW23" s="116">
         <v>-1811.6609251603193</v>
       </c>
       <c r="AX23" s="25">
@@ -3680,7 +5104,7 @@
       <c r="AY23" s="25">
         <v>-595.56121317661768</v>
       </c>
-      <c r="AZ23" s="25">
+      <c r="AZ23" s="116">
         <v>-1988.6088284197472</v>
       </c>
     </row>
@@ -3793,7 +5217,7 @@
       <c r="AJ24" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="AK24" s="27" t="s">
+      <c r="AK24" s="117" t="s">
         <v>39</v>
       </c>
       <c r="AL24" s="27" t="s">
@@ -3802,7 +5226,7 @@
       <c r="AM24" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="AN24" s="27" t="s">
+      <c r="AN24" s="117" t="s">
         <v>39</v>
       </c>
       <c r="AO24" s="27" t="s">
@@ -3811,7 +5235,7 @@
       <c r="AP24" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="AQ24" s="27" t="s">
+      <c r="AQ24" s="117" t="s">
         <v>39</v>
       </c>
       <c r="AR24" s="27" t="s">
@@ -3820,7 +5244,7 @@
       <c r="AS24" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="AT24" s="27" t="s">
+      <c r="AT24" s="117" t="s">
         <v>39</v>
       </c>
       <c r="AU24" s="27" t="s">
@@ -3829,7 +5253,7 @@
       <c r="AV24" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="AW24" s="27" t="s">
+      <c r="AW24" s="117" t="s">
         <v>39</v>
       </c>
       <c r="AX24" s="27" t="s">
@@ -3838,7 +5262,7 @@
       <c r="AY24" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="AZ24" s="27" t="s">
+      <c r="AZ24" s="117" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3893,22 +5317,22 @@
       <c r="AH25" s="30"/>
       <c r="AI25" s="31"/>
       <c r="AJ25" s="31"/>
-      <c r="AK25" s="31"/>
+      <c r="AK25" s="118"/>
       <c r="AL25" s="31"/>
       <c r="AM25" s="31"/>
-      <c r="AN25" s="31"/>
+      <c r="AN25" s="118"/>
       <c r="AO25" s="31"/>
       <c r="AP25" s="31"/>
-      <c r="AQ25" s="31"/>
+      <c r="AQ25" s="118"/>
       <c r="AR25" s="31"/>
       <c r="AS25" s="31"/>
-      <c r="AT25" s="31"/>
+      <c r="AT25" s="118"/>
       <c r="AU25" s="31"/>
       <c r="AV25" s="31"/>
-      <c r="AW25" s="31"/>
+      <c r="AW25" s="118"/>
       <c r="AX25" s="31"/>
       <c r="AY25" s="31"/>
-      <c r="AZ25" s="31"/>
+      <c r="AZ25" s="118"/>
     </row>
     <row r="26" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A26" s="13"/>
@@ -3993,22 +5417,22 @@
       <c r="AH26" s="25"/>
       <c r="AI26" s="25"/>
       <c r="AJ26" s="25"/>
-      <c r="AK26" s="25"/>
+      <c r="AK26" s="116"/>
       <c r="AL26" s="25"/>
       <c r="AM26" s="25"/>
-      <c r="AN26" s="25"/>
+      <c r="AN26" s="116"/>
       <c r="AO26" s="25"/>
       <c r="AP26" s="25"/>
-      <c r="AQ26" s="25"/>
+      <c r="AQ26" s="116"/>
       <c r="AR26" s="25"/>
       <c r="AS26" s="25"/>
-      <c r="AT26" s="25"/>
+      <c r="AT26" s="116"/>
       <c r="AU26" s="25"/>
       <c r="AV26" s="25"/>
-      <c r="AW26" s="25"/>
+      <c r="AW26" s="116"/>
       <c r="AX26" s="25"/>
       <c r="AY26" s="25"/>
-      <c r="AZ26" s="25"/>
+      <c r="AZ26" s="116"/>
     </row>
     <row r="27" spans="1:52" ht="16" x14ac:dyDescent="0.8">
       <c r="A27" s="13" t="s">
@@ -4119,7 +5543,7 @@
       <c r="AJ27" s="35">
         <v>11074</v>
       </c>
-      <c r="AK27" s="36">
+      <c r="AK27" s="119">
         <v>21512</v>
       </c>
       <c r="AL27" s="36">
@@ -4128,7 +5552,7 @@
       <c r="AM27" s="36">
         <v>12206.729454052709</v>
       </c>
-      <c r="AN27" s="36">
+      <c r="AN27" s="119">
         <v>24413.458908105418</v>
       </c>
       <c r="AO27" s="36">
@@ -4137,7 +5561,7 @@
       <c r="AP27" s="36">
         <v>13845.962183226446</v>
       </c>
-      <c r="AQ27" s="36">
+      <c r="AQ27" s="119">
         <v>27691.924366452891</v>
       </c>
       <c r="AR27" s="36">
@@ -4146,7 +5570,7 @@
       <c r="AS27" s="36">
         <v>15573.178828834545</v>
       </c>
-      <c r="AT27" s="36">
+      <c r="AT27" s="119">
         <v>31146.35765766909</v>
       </c>
       <c r="AU27" s="36">
@@ -4155,7 +5579,7 @@
       <c r="AV27" s="36">
         <v>17456.932599519041</v>
       </c>
-      <c r="AW27" s="36">
+      <c r="AW27" s="119">
         <v>34913.865199038082</v>
       </c>
       <c r="AX27" s="36">
@@ -4164,7 +5588,7 @@
       <c r="AY27" s="36">
         <v>19577.34137275321</v>
       </c>
-      <c r="AZ27" s="36">
+      <c r="AZ27" s="119">
         <v>39154.682745506419</v>
       </c>
     </row>
@@ -4277,7 +5701,7 @@
       <c r="AJ28" s="39">
         <v>0.16038579984665441</v>
       </c>
-      <c r="AK28" s="39">
+      <c r="AK28" s="120">
         <v>0.16546014323811883</v>
       </c>
       <c r="AL28" s="39">
@@ -4286,7 +5710,7 @@
       <c r="AM28" s="39">
         <v>0.17938021640550875</v>
       </c>
-      <c r="AN28" s="39">
+      <c r="AN28" s="120">
         <v>0.17626652465618078</v>
       </c>
       <c r="AO28" s="39">
@@ -4295,7 +5719,7 @@
       <c r="AP28" s="39">
         <v>0.18988120195443273</v>
       </c>
-      <c r="AQ28" s="39">
+      <c r="AQ28" s="120">
         <v>0.18383799968178346</v>
       </c>
       <c r="AR28" s="39">
@@ -4304,7 +5728,7 @@
       <c r="AS28" s="39">
         <v>0.19359754674764112</v>
       </c>
-      <c r="AT28" s="39">
+      <c r="AT28" s="120">
         <v>0.18786735635011592</v>
       </c>
       <c r="AU28" s="39">
@@ -4313,7 +5737,7 @@
       <c r="AV28" s="39">
         <v>0.19565371329252165</v>
       </c>
-      <c r="AW28" s="39">
+      <c r="AW28" s="120">
         <v>0.18985626615967205</v>
       </c>
       <c r="AX28" s="39">
@@ -4322,7 +5746,7 @@
       <c r="AY28" s="39">
         <v>0.19841380690425825</v>
       </c>
-      <c r="AZ28" s="39">
+      <c r="AZ28" s="120">
         <v>0.19254613324113448</v>
       </c>
     </row>
@@ -4435,7 +5859,7 @@
       <c r="AJ29" s="39">
         <v>0.18865090699938322</v>
       </c>
-      <c r="AK29" s="39">
+      <c r="AK29" s="120">
         <v>0.20053719230054018</v>
       </c>
       <c r="AL29" s="39">
@@ -4444,7 +5868,7 @@
       <c r="AM29" s="39">
         <v>0.19275029848561318</v>
       </c>
-      <c r="AN29" s="39">
+      <c r="AN29" s="120">
         <v>0.19544292641226998</v>
       </c>
       <c r="AO29" s="39">
@@ -4453,7 +5877,7 @@
       <c r="AP29" s="39">
         <v>0.17678547687735396</v>
       </c>
-      <c r="AQ29" s="39">
+      <c r="AQ29" s="120">
         <v>0.19708559679766124</v>
       </c>
       <c r="AR29" s="39">
@@ -4462,7 +5886,7 @@
       <c r="AS29" s="39">
         <v>0.18788494332962288</v>
       </c>
-      <c r="AT29" s="39">
+      <c r="AT29" s="120">
         <v>0.20500503475212281</v>
       </c>
       <c r="AU29" s="39">
@@ -4471,7 +5895,7 @@
       <c r="AV29" s="39">
         <v>0.19221900262116215</v>
       </c>
-      <c r="AW29" s="39">
+      <c r="AW29" s="120">
         <v>0.20621080279034229</v>
       </c>
       <c r="AX29" s="39">
@@ -4480,7 +5904,7 @@
       <c r="AY29" s="39">
         <v>0.19782906347200577</v>
       </c>
-      <c r="AZ29" s="39">
+      <c r="AZ29" s="120">
         <v>0.21126024180894573</v>
       </c>
     </row>
@@ -4593,7 +6017,7 @@
       <c r="AJ30" s="39">
         <v>4.595330829542054E-2</v>
       </c>
-      <c r="AK30" s="39">
+      <c r="AK30" s="120">
         <v>4.8267929014096267E-2</v>
       </c>
       <c r="AL30" s="39">
@@ -4602,7 +6026,7 @@
       <c r="AM30" s="39">
         <v>6.8464021255010693E-2</v>
       </c>
-      <c r="AN30" s="39">
+      <c r="AN30" s="120">
         <v>6.5305740908504314E-2</v>
       </c>
       <c r="AO30" s="39">
@@ -4611,7 +6035,7 @@
       <c r="AP30" s="39">
         <v>5.7522104816690109E-2</v>
       </c>
-      <c r="AQ30" s="39">
+      <c r="AQ30" s="120">
         <v>5.7506975131284256E-2</v>
       </c>
       <c r="AR30" s="39">
@@ -4620,7 +6044,7 @@
       <c r="AS30" s="39">
         <v>4.4717671027401498E-2</v>
       </c>
-      <c r="AT30" s="39">
+      <c r="AT30" s="120">
         <v>4.8938235172937043E-2</v>
       </c>
       <c r="AU30" s="39">
@@ -4629,7 +6053,7 @@
       <c r="AV30" s="39">
         <v>3.5500987718633741E-2</v>
       </c>
-      <c r="AW30" s="39">
+      <c r="AW30" s="120">
         <v>3.5534903705779032E-2</v>
       </c>
       <c r="AX30" s="39">
@@ -4638,7 +6062,7 @@
       <c r="AY30" s="39">
         <v>3.1001519033258772E-2</v>
       </c>
-      <c r="AZ30" s="39">
+      <c r="AZ30" s="120">
         <v>3.2074422687699104E-2</v>
       </c>
     </row>
@@ -4703,7 +6127,7 @@
       <c r="AJ31" s="39">
         <v>4.7535104091790681E-3</v>
       </c>
-      <c r="AK31" s="39">
+      <c r="AK31" s="120">
         <v>7.6216379010740978E-3</v>
       </c>
       <c r="AL31" s="39">
@@ -4712,7 +6136,7 @@
       <c r="AM31" s="39">
         <v>2.8400527733874879E-2</v>
       </c>
-      <c r="AN31" s="39">
+      <c r="AN31" s="120">
         <v>2.426235405315183E-2</v>
       </c>
       <c r="AO31" s="39">
@@ -4721,7 +6145,7 @@
       <c r="AP31" s="39">
         <v>1.9702767000169794E-2</v>
       </c>
-      <c r="AQ31" s="39">
+      <c r="AQ31" s="120">
         <v>1.8456095568033321E-2</v>
       </c>
       <c r="AR31" s="39">
@@ -4730,7 +6154,7 @@
       <c r="AS31" s="39">
         <v>9.9278699061364564E-3</v>
       </c>
-      <c r="AT31" s="39">
+      <c r="AT31" s="120">
         <v>1.3338318225031951E-2</v>
       </c>
       <c r="AU31" s="39">
@@ -4739,7 +6163,7 @@
       <c r="AV31" s="39">
         <v>2.0426379304576284E-3</v>
       </c>
-      <c r="AW31" s="39">
+      <c r="AW31" s="120">
         <v>2.0068315060444027E-3</v>
       </c>
       <c r="AX31" s="39">
@@ -4748,7 +6172,7 @@
       <c r="AY31" s="39">
         <v>1.7328784205783835E-3</v>
       </c>
-      <c r="AZ31" s="39">
+      <c r="AZ31" s="120">
         <v>1.6801053432437812E-3</v>
       </c>
     </row>
@@ -4813,7 +6237,7 @@
       <c r="AJ32" s="39">
         <v>2.4562037204262231E-3</v>
       </c>
-      <c r="AK32" s="39">
+      <c r="AK32" s="120">
         <v>1.6804617246653031E-3</v>
       </c>
       <c r="AL32" s="39">
@@ -4822,7 +6246,7 @@
       <c r="AM32" s="39">
         <v>2.5897191552046436E-2</v>
       </c>
-      <c r="AN32" s="39">
+      <c r="AN32" s="120">
         <v>2.1759017871323384E-2</v>
       </c>
       <c r="AO32" s="39">
@@ -4831,7 +6255,7 @@
       <c r="AP32" s="39">
         <v>1.8529000864775096E-2</v>
       </c>
-      <c r="AQ32" s="39">
+      <c r="AQ32" s="120">
         <v>1.7282329432638625E-2</v>
       </c>
       <c r="AR32" s="39">
@@ -4840,7 +6264,7 @@
       <c r="AS32" s="39">
         <v>8.9633821380907044E-3</v>
       </c>
-      <c r="AT32" s="39">
+      <c r="AT32" s="120">
         <v>1.2373830456986199E-2</v>
       </c>
       <c r="AU32" s="39">
@@ -4849,7 +6273,7 @@
       <c r="AV32" s="39">
         <v>1.1478102727034605E-3</v>
       </c>
-      <c r="AW32" s="39">
+      <c r="AW32" s="120">
         <v>1.1464202966653949E-3</v>
       </c>
       <c r="AX32" s="39">
@@ -4858,7 +6282,7 @@
       <c r="AY32" s="39">
         <v>9.6548223696638969E-4</v>
       </c>
-      <c r="AZ32" s="39">
+      <c r="AZ32" s="120">
         <v>9.4222439746301809E-4</v>
       </c>
     </row>
@@ -4971,7 +6395,7 @@
       <c r="AJ33" s="39">
         <v>0.23460421529480377</v>
       </c>
-      <c r="AK33" s="39">
+      <c r="AK33" s="120">
         <v>0.24880512131463645</v>
       </c>
       <c r="AL33" s="39">
@@ -4980,7 +6404,7 @@
       <c r="AM33" s="39">
         <v>0.26121431974062387</v>
       </c>
-      <c r="AN33" s="39">
+      <c r="AN33" s="120">
         <v>0.26074866732077423</v>
       </c>
       <c r="AO33" s="39">
@@ -4989,7 +6413,7 @@
       <c r="AP33" s="39">
         <v>0.23431016217694042</v>
       </c>
-      <c r="AQ33" s="39">
+      <c r="AQ33" s="120">
         <v>0.25459257192894552</v>
       </c>
       <c r="AR33" s="39">
@@ -4998,7 +6422,7 @@
       <c r="AS33" s="39">
         <v>0.23260095030221645</v>
       </c>
-      <c r="AT33" s="39">
+      <c r="AT33" s="120">
         <v>0.25394326992505989</v>
       </c>
       <c r="AU33" s="39">
@@ -5007,7 +6431,7 @@
       <c r="AV33" s="39">
         <v>0.22772059125071548</v>
       </c>
-      <c r="AW33" s="39">
+      <c r="AW33" s="120">
         <v>0.24174570649612137</v>
       </c>
       <c r="AX33" s="39">
@@ -5016,7 +6440,7 @@
       <c r="AY33" s="39">
         <v>0.22883475129283029</v>
       </c>
-      <c r="AZ33" s="39">
+      <c r="AZ33" s="120">
         <v>0.24333466449664484</v>
       </c>
     </row>
@@ -5129,7 +6553,7 @@
       <c r="AJ34" s="39">
         <v>-7.4218415448149333E-2</v>
       </c>
-      <c r="AK34" s="39">
+      <c r="AK34" s="120">
         <v>-8.3344978076517584E-2</v>
       </c>
       <c r="AL34" s="39">
@@ -5138,7 +6562,7 @@
       <c r="AM34" s="39">
         <v>-8.183410333511508E-2</v>
       </c>
-      <c r="AN34" s="39">
+      <c r="AN34" s="120">
         <v>-8.4482142664593501E-2</v>
       </c>
       <c r="AO34" s="39">
@@ -5147,7 +6571,7 @@
       <c r="AP34" s="39">
         <v>-4.4428960222507669E-2</v>
       </c>
-      <c r="AQ34" s="39">
+      <c r="AQ34" s="120">
         <v>-7.0754572247162029E-2</v>
       </c>
       <c r="AR34" s="39">
@@ -5156,7 +6580,7 @@
       <c r="AS34" s="39">
         <v>-3.9003403554575287E-2</v>
       </c>
-      <c r="AT34" s="39">
+      <c r="AT34" s="120">
         <v>-6.6075913574943954E-2</v>
       </c>
       <c r="AU34" s="39">
@@ -5165,7 +6589,7 @@
       <c r="AV34" s="39">
         <v>-3.2066877958193851E-2</v>
       </c>
-      <c r="AW34" s="39">
+      <c r="AW34" s="120">
         <v>-5.1889440336449273E-2</v>
       </c>
       <c r="AX34" s="39">
@@ -5174,7 +6598,7 @@
       <c r="AY34" s="39">
         <v>-3.0420944388572128E-2</v>
       </c>
-      <c r="AZ34" s="39">
+      <c r="AZ34" s="120">
         <v>-5.0788531255510416E-2</v>
       </c>
     </row>
@@ -5249,9 +6673,8 @@
       </c>
       <c r="AX36" s="45"/>
       <c r="AY36" s="45"/>
-      <c r="AZ36" s="43" t="str">
-        <f>+AZ5</f>
-        <v>2029/2030</v>
+      <c r="AZ36" s="43">
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:52" ht="16" x14ac:dyDescent="0.8">
@@ -5267,7 +6690,7 @@
         <f t="shared" si="0"/>
         <v>-7.4218415448149333E-2</v>
       </c>
-      <c r="AK37" s="47">
+      <c r="AK37" s="78">
         <f>+AK34</f>
         <v>-8.3344978076517584E-2</v>
       </c>
@@ -5279,7 +6702,7 @@
         <f t="shared" si="1"/>
         <v>-8.183410333511508E-2</v>
       </c>
-      <c r="AN37" s="47">
+      <c r="AN37" s="78">
         <f t="shared" si="1"/>
         <v>-8.4482142664593501E-2</v>
       </c>
@@ -5291,7 +6714,7 @@
         <f t="shared" si="1"/>
         <v>-4.4428960222507669E-2</v>
       </c>
-      <c r="AQ37" s="47">
+      <c r="AQ37" s="78">
         <f t="shared" si="1"/>
         <v>-7.0754572247162029E-2</v>
       </c>
@@ -5303,7 +6726,7 @@
         <f t="shared" si="1"/>
         <v>-3.9003403554575287E-2</v>
       </c>
-      <c r="AT37" s="47">
+      <c r="AT37" s="78">
         <f t="shared" si="1"/>
         <v>-6.6075913574943954E-2</v>
       </c>
@@ -5315,7 +6738,7 @@
         <f t="shared" si="1"/>
         <v>-3.2066877958193851E-2</v>
       </c>
-      <c r="AW37" s="47">
+      <c r="AW37" s="78">
         <f t="shared" si="1"/>
         <v>-5.1889440336449273E-2</v>
       </c>
@@ -5327,13 +6750,13 @@
         <f t="shared" si="1"/>
         <v>-3.0420944388572128E-2</v>
       </c>
-      <c r="AZ37" s="47">
+      <c r="AZ37" s="78">
         <f t="shared" si="1"/>
         <v>-5.0788531255510416E-2</v>
       </c>
     </row>
     <row r="38" spans="1:52" x14ac:dyDescent="0.75">
-      <c r="A38" s="97" t="str">
+      <c r="A38" s="93" t="str">
         <f>+A51</f>
         <v xml:space="preserve">correction </v>
       </c>
@@ -5345,7 +6768,7 @@
         <f t="shared" ref="AM38:AZ38" si="2">-AM51</f>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="AN38" s="48">
+      <c r="AN38" s="94">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5357,7 +6780,7 @@
         <f t="shared" si="2"/>
         <v>-0.02</v>
       </c>
-      <c r="AQ38" s="48">
+      <c r="AQ38" s="94">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5369,7 +6792,7 @@
         <f t="shared" si="2"/>
         <v>-1.7999999999999999E-2</v>
       </c>
-      <c r="AT38" s="48">
+      <c r="AT38" s="94">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5381,7 +6804,7 @@
         <f t="shared" si="2"/>
         <v>-1.4999999999999999E-2</v>
       </c>
-      <c r="AW38" s="48">
+      <c r="AW38" s="94">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5393,7 +6816,7 @@
         <f t="shared" si="2"/>
         <v>-1.4999999999999999E-2</v>
       </c>
-      <c r="AZ38" s="48">
+      <c r="AZ38" s="94">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5410,7 +6833,7 @@
         <f t="shared" ref="AM39:AZ39" si="3">+AM37+AM38</f>
         <v>-8.6834103335115084E-2</v>
       </c>
-      <c r="AN39" s="50">
+      <c r="AN39" s="121">
         <f t="shared" si="3"/>
         <v>-8.4482142664593501E-2</v>
       </c>
@@ -5422,7 +6845,7 @@
         <f t="shared" si="3"/>
         <v>-6.4428960222507672E-2</v>
       </c>
-      <c r="AQ39" s="50">
+      <c r="AQ39" s="121">
         <f t="shared" si="3"/>
         <v>-7.0754572247162029E-2</v>
       </c>
@@ -5434,7 +6857,7 @@
         <f t="shared" si="3"/>
         <v>-5.7003403554575283E-2</v>
       </c>
-      <c r="AT39" s="50">
+      <c r="AT39" s="121">
         <f t="shared" si="3"/>
         <v>-6.6075913574943954E-2</v>
       </c>
@@ -5446,7 +6869,7 @@
         <f t="shared" si="3"/>
         <v>-4.7066877958193851E-2</v>
       </c>
-      <c r="AW39" s="50">
+      <c r="AW39" s="121">
         <f t="shared" si="3"/>
         <v>-5.1889440336449273E-2</v>
       </c>
@@ -5458,7 +6881,7 @@
         <f t="shared" si="3"/>
         <v>-4.5420944388572124E-2</v>
       </c>
-      <c r="AZ39" s="50">
+      <c r="AZ39" s="121">
         <f t="shared" si="3"/>
         <v>-5.0788531255510416E-2</v>
       </c>
@@ -5475,8 +6898,8 @@
         <f>+AM46-AM53-AM60</f>
         <v>-8.8714319740623854E-2</v>
       </c>
-      <c r="AN40" s="53"/>
-      <c r="AO40" s="54">
+      <c r="AN40" s="137"/>
+      <c r="AO40" s="53">
         <f>+AO46-AO53-AO60</f>
         <v>-7.4877562163846931E-2</v>
       </c>
@@ -5484,28 +6907,28 @@
         <f>+AP46-AP53-AP60</f>
         <v>-6.9307581694044038E-2</v>
       </c>
-      <c r="AQ40" s="53"/>
-      <c r="AR40" s="54">
+      <c r="AQ40" s="137"/>
+      <c r="AR40" s="53">
         <f>+AR46-AR53-AR60</f>
         <v>-7.1283925493095313E-2</v>
       </c>
-      <c r="AS40" s="55">
+      <c r="AS40" s="54">
         <f>+AS46-AS53-AS60</f>
         <v>-6.3102614357024342E-2</v>
       </c>
-      <c r="AU40" s="56">
+      <c r="AU40" s="55">
         <f>+AU46-AU53-AU60</f>
         <v>-5.2071422652446762E-2</v>
       </c>
-      <c r="AV40" s="57">
+      <c r="AV40" s="56">
         <f>+AV46-AV53-AV60</f>
         <v>-5.1819990339795861E-2</v>
       </c>
-      <c r="AX40" s="56">
+      <c r="AX40" s="55">
         <f>+AX46-AX53-AX60</f>
         <v>-5.0438746488025224E-2</v>
       </c>
-      <c r="AY40" s="57">
+      <c r="AY40" s="56">
         <f>+AY46-AY53-AY60</f>
         <v>-5.0430582505264485E-2</v>
       </c>
@@ -5514,70 +6937,70 @@
       <c r="A41" t="s">
         <v>44</v>
       </c>
-      <c r="AL41" s="58">
+      <c r="AL41" s="57">
         <f>+AL47-AL54-AL61</f>
         <v>-8.0283014900924737E-2</v>
       </c>
-      <c r="AM41" s="59">
+      <c r="AM41" s="58">
         <f>+AM47-AM54-AM61</f>
         <v>-8.6214319740623852E-2</v>
       </c>
-      <c r="AN41" s="60" t="str">
+      <c r="AN41" s="124" t="str">
         <f>IF(ABS(AVERAGE(AL40:AM41)-AN39)&gt;0.001,"check","")</f>
         <v/>
       </c>
-      <c r="AO41" s="61">
+      <c r="AO41" s="59">
         <f>+AO47-AO54-AO61</f>
         <v>-7.387756216384693E-2</v>
       </c>
-      <c r="AP41" s="59">
+      <c r="AP41" s="58">
         <f>+AP47-AP54-AP61</f>
         <v>-6.5307581694044034E-2</v>
       </c>
-      <c r="AQ41" s="60" t="str">
+      <c r="AQ41" s="124" t="str">
         <f>IF(ABS(AVERAGE(AO40:AP41)-AQ39)&gt;0.001,"check","")</f>
         <v/>
       </c>
-      <c r="AR41" s="61">
+      <c r="AR41" s="59">
         <f>+AR47-AR54-AR61</f>
         <v>-7.0283925493095312E-2</v>
       </c>
-      <c r="AS41" s="62">
+      <c r="AS41" s="60">
         <f>+AS47-AS54-AS61</f>
         <v>-6.2602614357024342E-2</v>
       </c>
-      <c r="AT41" s="63" t="str">
+      <c r="AT41" s="122" t="str">
         <f>IF(ABS(AVERAGE(AR40:AS41)-AT39)&gt;0.001,"check","")</f>
         <v/>
       </c>
-      <c r="AU41" s="56">
+      <c r="AU41" s="55">
         <f>+AU47-AU54-AU61</f>
         <v>-5.1371422652446756E-2</v>
       </c>
-      <c r="AV41" s="57">
+      <c r="AV41" s="56">
         <f>+AV47-AV54-AV61</f>
         <v>-5.031999033979586E-2</v>
       </c>
-      <c r="AW41" s="64" t="str">
+      <c r="AW41" s="135" t="str">
         <f>IF(ABS(AVERAGE(AU40:AV41)-AW39)&gt;0.001,"check","")</f>
         <v/>
       </c>
-      <c r="AX41" s="56">
+      <c r="AX41" s="55">
         <f>+AX47-AX54-AX61</f>
         <v>-5.0438746488025224E-2</v>
       </c>
-      <c r="AY41" s="57">
+      <c r="AY41" s="56">
         <f>+AY47-AY54-AY61</f>
         <v>-4.9430582505264484E-2</v>
       </c>
-      <c r="AZ41" s="64" t="str">
+      <c r="AZ41" s="135" t="str">
         <f>IF(ABS(AVERAGE(AX40:AY41)-AZ39)&gt;0.001,"check","")</f>
         <v/>
       </c>
     </row>
     <row r="42" spans="1:52" ht="15.5" thickTop="1" x14ac:dyDescent="0.75"/>
     <row r="43" spans="1:52" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A43" s="65" t="str">
+      <c r="A43" s="61" t="str">
         <f>+A28</f>
         <v>Grev in % of GDP</v>
       </c>
@@ -5589,7 +7012,7 @@
         <f t="shared" si="4"/>
         <v>0.16038579984665441</v>
       </c>
-      <c r="AK43" s="15">
+      <c r="AK43" s="114">
         <f t="shared" si="4"/>
         <v>0.16546014323811883</v>
       </c>
@@ -5601,7 +7024,7 @@
         <f t="shared" si="4"/>
         <v>0.17938021640550875</v>
       </c>
-      <c r="AN43" s="15">
+      <c r="AN43" s="114">
         <f t="shared" si="4"/>
         <v>0.17626652465618078</v>
       </c>
@@ -5613,7 +7036,7 @@
         <f t="shared" si="4"/>
         <v>0.18988120195443273</v>
       </c>
-      <c r="AQ43" s="15">
+      <c r="AQ43" s="114">
         <f t="shared" si="4"/>
         <v>0.18383799968178346</v>
       </c>
@@ -5625,7 +7048,7 @@
         <f t="shared" si="4"/>
         <v>0.19359754674764112</v>
       </c>
-      <c r="AT43" s="15">
+      <c r="AT43" s="114">
         <f t="shared" si="4"/>
         <v>0.18786735635011592</v>
       </c>
@@ -5637,7 +7060,7 @@
         <f t="shared" si="4"/>
         <v>0.19565371329252165</v>
       </c>
-      <c r="AW43" s="15">
+      <c r="AW43" s="114">
         <f t="shared" si="4"/>
         <v>0.18985626615967205</v>
       </c>
@@ -5649,19 +7072,19 @@
         <f t="shared" si="4"/>
         <v>0.19841380690425825</v>
       </c>
-      <c r="AZ43" s="15">
+      <c r="AZ43" s="114">
         <f t="shared" si="4"/>
         <v>0.19254613324113448</v>
       </c>
     </row>
     <row r="44" spans="1:52" ht="16.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A44" s="97" t="str">
+      <c r="A44" s="93" t="str">
         <f>+A51</f>
         <v xml:space="preserve">correction </v>
       </c>
       <c r="AI44" s="15"/>
       <c r="AJ44" s="15"/>
-      <c r="AK44" s="15"/>
+      <c r="AK44" s="114"/>
       <c r="AL44" s="48">
         <v>0</v>
       </c>
@@ -5669,51 +7092,51 @@
         <f>-AL44</f>
         <v>0</v>
       </c>
-      <c r="AN44" s="48">
+      <c r="AN44" s="94">
         <f>+AL44+AM44</f>
         <v>0</v>
       </c>
-      <c r="AO44" s="100">
+      <c r="AO44" s="94">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="AP44" s="100">
+      <c r="AP44" s="94">
         <f>-AO44</f>
         <v>-3.0000000000000001E-3</v>
       </c>
-      <c r="AQ44" s="48">
+      <c r="AQ44" s="94">
         <f>+AO44+AP44</f>
         <v>0</v>
       </c>
-      <c r="AR44" s="100">
+      <c r="AR44" s="94">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="AS44" s="100">
+      <c r="AS44" s="94">
         <f>-AR44</f>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="AT44" s="48">
+      <c r="AT44" s="94">
         <f>+AR44+AS44</f>
         <v>0</v>
       </c>
-      <c r="AU44" s="100">
+      <c r="AU44" s="94">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="AV44" s="100">
+      <c r="AV44" s="94">
         <f>-AU44</f>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="AW44" s="48">
+      <c r="AW44" s="94">
         <f>+AU44+AV44</f>
         <v>0</v>
       </c>
-      <c r="AX44" s="100">
+      <c r="AX44" s="94">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="AY44" s="100">
+      <c r="AY44" s="94">
         <f>-AX44</f>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="AZ44" s="48">
+      <c r="AZ44" s="94">
         <f>+AX44+AY44</f>
         <v>0</v>
       </c>
@@ -5724,7 +7147,7 @@
       </c>
       <c r="AI45" s="15"/>
       <c r="AJ45" s="15"/>
-      <c r="AK45" s="15">
+      <c r="AK45" s="114">
         <f>+AK43</f>
         <v>0.16546014323811883</v>
       </c>
@@ -5736,7 +7159,7 @@
         <f t="shared" ref="AM45:AN45" si="5">+AM43+AM44</f>
         <v>0.17938021640550875</v>
       </c>
-      <c r="AN45" s="50">
+      <c r="AN45" s="121">
         <f t="shared" si="5"/>
         <v>0.17626652465618078</v>
       </c>
@@ -5748,7 +7171,7 @@
         <f t="shared" ref="AP45:AQ45" si="6">+AP43+AP44</f>
         <v>0.18688120195443272</v>
       </c>
-      <c r="AQ45" s="50">
+      <c r="AQ45" s="121">
         <f t="shared" si="6"/>
         <v>0.18383799968178346</v>
       </c>
@@ -5760,7 +7183,7 @@
         <f t="shared" ref="AS45:AT45" si="7">+AS43+AS44</f>
         <v>0.18859754674764112</v>
       </c>
-      <c r="AT45" s="50">
+      <c r="AT45" s="121">
         <f t="shared" si="7"/>
         <v>0.18786735635011592</v>
       </c>
@@ -5772,7 +7195,7 @@
         <f t="shared" ref="AV45:AW45" si="8">+AV43+AV44</f>
         <v>0.19065371329252165</v>
       </c>
-      <c r="AW45" s="50">
+      <c r="AW45" s="121">
         <f t="shared" si="8"/>
         <v>0.18985626615967205</v>
       </c>
@@ -5784,7 +7207,7 @@
         <f t="shared" ref="AY45:AZ45" si="9">+AY43+AY44</f>
         <v>0.19341380690425825</v>
       </c>
-      <c r="AZ45" s="50">
+      <c r="AZ45" s="121">
         <f t="shared" si="9"/>
         <v>0.19254613324113448</v>
       </c>
@@ -5793,15 +7216,15 @@
       <c r="A46" t="s">
         <v>45</v>
       </c>
-      <c r="AI46" s="57">
+      <c r="AI46" s="56">
         <f>+AI43-AI48</f>
         <v>0.16884367252697466</v>
       </c>
-      <c r="AJ46" s="57">
+      <c r="AJ46" s="56">
         <f>+AI47+AJ48</f>
         <v>0.16434367252697465</v>
       </c>
-      <c r="AK46" s="56"/>
+      <c r="AK46" s="123"/>
       <c r="AL46" s="51">
         <v>0.17</v>
       </c>
@@ -5809,8 +7232,8 @@
         <f>+AL47+AM48</f>
         <v>0.17750000000000002</v>
       </c>
-      <c r="AN46" s="54"/>
-      <c r="AO46" s="54">
+      <c r="AN46" s="138"/>
+      <c r="AO46" s="53">
         <f>+AM47</f>
         <v>0.18000000000000002</v>
       </c>
@@ -5818,196 +7241,196 @@
         <f>+AO47+AP48</f>
         <v>0.18500000000000003</v>
       </c>
-      <c r="AQ46" s="54"/>
-      <c r="AR46" s="54">
+      <c r="AQ46" s="138"/>
+      <c r="AR46" s="53">
         <f>+AP47-0.003</f>
         <v>0.18600000000000003</v>
       </c>
-      <c r="AS46" s="55">
+      <c r="AS46" s="54">
         <f>+AR47+AS48</f>
         <v>0.18750000000000003</v>
       </c>
-      <c r="AT46" s="56"/>
-      <c r="AU46" s="56">
+      <c r="AT46" s="123"/>
+      <c r="AU46" s="55">
         <f>+AS47+AU48</f>
         <v>0.18870000000000003</v>
       </c>
-      <c r="AV46" s="57">
+      <c r="AV46" s="56">
         <f>+AU47+AV48</f>
         <v>0.19090000000000004</v>
       </c>
-      <c r="AW46" s="56"/>
-      <c r="AX46" s="56">
+      <c r="AW46" s="123"/>
+      <c r="AX46" s="55">
         <f>+AV47+AX48</f>
         <v>0.19240000000000004</v>
       </c>
-      <c r="AY46" s="57">
+      <c r="AY46" s="56">
         <f>+AX47+AY48</f>
         <v>0.19340000000000004</v>
       </c>
-      <c r="AZ46" s="15"/>
+      <c r="AZ46" s="114"/>
     </row>
     <row r="47" spans="1:52" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A47" t="s">
         <v>46</v>
       </c>
-      <c r="AI47" s="57">
+      <c r="AI47" s="56">
         <f>+AI43+AI48</f>
         <v>0.17284367252697466</v>
       </c>
-      <c r="AJ47" s="57">
+      <c r="AJ47" s="56">
         <f>+AJ46+AJ48</f>
         <v>0.15584367252697465</v>
       </c>
-      <c r="AK47" s="60" t="str">
+      <c r="AK47" s="124" t="str">
         <f>IF(ABS(AVERAGE(AI46:AJ47)-AK45)&gt;0.1,"check","")</f>
         <v/>
       </c>
-      <c r="AL47" s="58">
+      <c r="AL47" s="57">
         <f>+AL46+AL48</f>
         <v>0.17500000000000002</v>
       </c>
-      <c r="AM47" s="59">
+      <c r="AM47" s="58">
         <f>+AM46+AM48</f>
         <v>0.18000000000000002</v>
       </c>
-      <c r="AN47" s="60" t="str">
+      <c r="AN47" s="124" t="str">
         <f>IF(ABS(AVERAGE(AL46:AM47)-AN45)&gt;0.001,"check","")</f>
         <v/>
       </c>
-      <c r="AO47" s="61">
+      <c r="AO47" s="59">
         <f>+AO46+AO48</f>
         <v>0.18100000000000002</v>
       </c>
-      <c r="AP47" s="59">
+      <c r="AP47" s="58">
         <f>+AP46+AP48</f>
         <v>0.18900000000000003</v>
       </c>
-      <c r="AQ47" s="60" t="str">
+      <c r="AQ47" s="124" t="str">
         <f>IF(ABS(AVERAGE(AO46:AP47)-AQ45)&gt;0.001,"check","")</f>
         <v/>
       </c>
-      <c r="AR47" s="61">
+      <c r="AR47" s="59">
         <f>+AR46+AR48</f>
         <v>0.18700000000000003</v>
       </c>
-      <c r="AS47" s="62">
+      <c r="AS47" s="60">
         <f>+AS46+AS48</f>
         <v>0.18800000000000003</v>
       </c>
-      <c r="AT47" s="60" t="str">
+      <c r="AT47" s="124" t="str">
         <f>IF(ABS(AVERAGE(AR46:AS47)-AT45)&gt;0.001,"check","")</f>
         <v/>
       </c>
-      <c r="AU47" s="56">
+      <c r="AU47" s="55">
         <f>+AU46+AU48</f>
         <v>0.18940000000000004</v>
       </c>
-      <c r="AV47" s="57">
+      <c r="AV47" s="56">
         <f>+AV46+AV48</f>
         <v>0.19240000000000004</v>
       </c>
-      <c r="AW47" s="60" t="str">
+      <c r="AW47" s="124" t="str">
         <f>IF(ABS(AVERAGE(AU46:AV47)-AW45)&gt;0.001,"check","")</f>
         <v/>
       </c>
-      <c r="AX47" s="56">
+      <c r="AX47" s="55">
         <f>+AX46+AX48</f>
         <v>0.19240000000000004</v>
       </c>
-      <c r="AY47" s="57">
+      <c r="AY47" s="56">
         <f>+AY46+AY48</f>
         <v>0.19440000000000004</v>
       </c>
-      <c r="AZ47" s="60" t="str">
+      <c r="AZ47" s="124" t="str">
         <f>IF(ABS(AVERAGE(AX46:AY47)-AZ45)&gt;0.001,"check","")</f>
         <v/>
       </c>
     </row>
     <row r="48" spans="1:52" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
-      <c r="AI48" s="66">
+      <c r="AI48" s="62">
         <v>2E-3</v>
       </c>
-      <c r="AJ48" s="66">
+      <c r="AJ48" s="62">
         <v>-8.5000000000000006E-3</v>
       </c>
-      <c r="AK48" s="66">
+      <c r="AK48" s="125">
         <f>+AVERAGE(AI46:AJ47)</f>
         <v>0.16546867252697464</v>
       </c>
-      <c r="AL48" s="66">
+      <c r="AL48" s="62">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="AM48" s="66">
+      <c r="AM48" s="62">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="AN48" s="66">
+      <c r="AN48" s="125">
         <f>+AVERAGE(AL46:AM47)</f>
         <v>0.17562500000000003</v>
       </c>
-      <c r="AO48" s="66">
+      <c r="AO48" s="62">
         <v>1E-3</v>
       </c>
-      <c r="AP48" s="66">
+      <c r="AP48" s="62">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="AQ48" s="66">
+      <c r="AQ48" s="125">
         <f>+AVERAGE(AO46:AP47)</f>
         <v>0.18375000000000002</v>
       </c>
-      <c r="AR48" s="66">
+      <c r="AR48" s="62">
         <v>1E-3</v>
       </c>
-      <c r="AS48" s="66">
+      <c r="AS48" s="62">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="AT48" s="66">
+      <c r="AT48" s="125">
         <f>+AVERAGE(AR46:AS47)</f>
         <v>0.18712500000000004</v>
       </c>
-      <c r="AU48" s="66">
+      <c r="AU48" s="62">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="AV48" s="66">
+      <c r="AV48" s="62">
         <v>1.5E-3</v>
       </c>
-      <c r="AW48" s="66">
+      <c r="AW48" s="125">
         <f>+AVERAGE(AU46:AV47)</f>
         <v>0.19035000000000002</v>
       </c>
-      <c r="AX48" s="66">
+      <c r="AX48" s="62">
         <v>0</v>
       </c>
-      <c r="AY48" s="66">
+      <c r="AY48" s="62">
         <v>1E-3</v>
       </c>
-      <c r="AZ48" s="66">
+      <c r="AZ48" s="125">
         <f>+AVERAGE(AX46:AY47)</f>
         <v>0.19315000000000004</v>
       </c>
     </row>
     <row r="49" spans="1:55" x14ac:dyDescent="0.75">
-      <c r="AI49" s="66"/>
-      <c r="AJ49" s="66"/>
-      <c r="AK49" s="66"/>
-      <c r="AL49" s="66"/>
-      <c r="AM49" s="66"/>
-      <c r="AN49" s="66"/>
-      <c r="AO49" s="66"/>
-      <c r="AP49" s="66"/>
-      <c r="AQ49" s="66"/>
-      <c r="AR49" s="66"/>
-      <c r="AS49" s="66"/>
-      <c r="AT49" s="66"/>
-      <c r="AU49" s="66"/>
-      <c r="AV49" s="66"/>
-      <c r="AW49" s="66"/>
-      <c r="AX49" s="66"/>
-      <c r="AY49" s="66"/>
-      <c r="AZ49" s="66"/>
+      <c r="AI49" s="62"/>
+      <c r="AJ49" s="62"/>
+      <c r="AK49" s="125"/>
+      <c r="AL49" s="62"/>
+      <c r="AM49" s="62"/>
+      <c r="AN49" s="125"/>
+      <c r="AO49" s="62"/>
+      <c r="AP49" s="62"/>
+      <c r="AQ49" s="125"/>
+      <c r="AR49" s="62"/>
+      <c r="AS49" s="62"/>
+      <c r="AT49" s="125"/>
+      <c r="AU49" s="62"/>
+      <c r="AV49" s="62"/>
+      <c r="AW49" s="125"/>
+      <c r="AX49" s="62"/>
+      <c r="AY49" s="62"/>
+      <c r="AZ49" s="125"/>
     </row>
     <row r="50" spans="1:55" ht="15.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A50" s="65" t="str">
+      <c r="A50" s="61" t="str">
         <f>+A29</f>
         <v>Gdem in % of GDP</v>
       </c>
@@ -6019,7 +7442,7 @@
         <f t="shared" si="10"/>
         <v>0.18865090699938322</v>
       </c>
-      <c r="AK50" s="15">
+      <c r="AK50" s="114">
         <f t="shared" si="10"/>
         <v>0.20053719230054018</v>
       </c>
@@ -6031,7 +7454,7 @@
         <f t="shared" si="10"/>
         <v>0.19275029848561318</v>
       </c>
-      <c r="AN50" s="15">
+      <c r="AN50" s="114">
         <f t="shared" si="10"/>
         <v>0.19544292641226998</v>
       </c>
@@ -6043,7 +7466,7 @@
         <f t="shared" si="10"/>
         <v>0.17678547687735396</v>
       </c>
-      <c r="AQ50" s="15">
+      <c r="AQ50" s="114">
         <f t="shared" si="10"/>
         <v>0.19708559679766124</v>
       </c>
@@ -6055,7 +7478,7 @@
         <f t="shared" si="10"/>
         <v>0.18788494332962288</v>
       </c>
-      <c r="AT50" s="15">
+      <c r="AT50" s="114">
         <f t="shared" si="10"/>
         <v>0.20500503475212281</v>
       </c>
@@ -6067,7 +7490,7 @@
         <f t="shared" si="10"/>
         <v>0.19221900262116215</v>
       </c>
-      <c r="AW50" s="15">
+      <c r="AW50" s="114">
         <f t="shared" si="10"/>
         <v>0.20621080279034229</v>
       </c>
@@ -6079,78 +7502,78 @@
         <f t="shared" si="10"/>
         <v>0.19782906347200577</v>
       </c>
-      <c r="AZ50" s="15">
+      <c r="AZ50" s="114">
         <f t="shared" si="10"/>
         <v>0.21126024180894573</v>
       </c>
     </row>
     <row r="51" spans="1:55" x14ac:dyDescent="0.75">
-      <c r="A51" s="67" t="s">
+      <c r="A51" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="AI51" s="68">
+      <c r="AI51" s="64">
         <v>0</v>
       </c>
-      <c r="AJ51" s="68">
+      <c r="AJ51" s="64">
         <f>-AI51</f>
         <v>0</v>
       </c>
-      <c r="AK51" s="68">
+      <c r="AK51" s="95">
         <f>+AI51+AJ51</f>
         <v>0</v>
       </c>
-      <c r="AL51" s="100">
+      <c r="AL51" s="94">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="AM51" s="100">
+      <c r="AM51" s="94">
         <f>-AL51</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="AN51" s="68">
+      <c r="AN51" s="95">
         <f>+AL51+AM51</f>
         <v>0</v>
       </c>
-      <c r="AO51" s="101">
+      <c r="AO51" s="95">
         <v>-0.02</v>
       </c>
-      <c r="AP51" s="101">
+      <c r="AP51" s="95">
         <f>-AO51</f>
         <v>0.02</v>
       </c>
-      <c r="AQ51" s="68">
+      <c r="AQ51" s="95">
         <f>+AO51+AP51</f>
         <v>0</v>
       </c>
-      <c r="AR51" s="100">
+      <c r="AR51" s="94">
         <v>-1.7999999999999999E-2</v>
       </c>
-      <c r="AS51" s="100">
+      <c r="AS51" s="94">
         <f>-AR51</f>
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="AT51" s="68">
+      <c r="AT51" s="95">
         <f>+AR51+AS51</f>
         <v>0</v>
       </c>
-      <c r="AU51" s="100">
+      <c r="AU51" s="94">
         <v>-1.4999999999999999E-2</v>
       </c>
-      <c r="AV51" s="100">
+      <c r="AV51" s="94">
         <f>-AU51</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="AW51" s="68">
+      <c r="AW51" s="95">
         <f>+AU51+AV51</f>
         <v>0</v>
       </c>
-      <c r="AX51" s="100">
+      <c r="AX51" s="94">
         <v>-1.4999999999999999E-2</v>
       </c>
-      <c r="AY51" s="100">
+      <c r="AY51" s="94">
         <f>-AX51</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="AZ51" s="68">
+      <c r="AZ51" s="95">
         <f>+AX51+AY51</f>
         <v>0</v>
       </c>
@@ -6159,75 +7582,75 @@
       <c r="A52" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="AI52" s="69">
+      <c r="AI52" s="65">
         <f t="shared" ref="AI52:AZ52" si="11">+AI50+AI51</f>
         <v>0.21314772338168717</v>
       </c>
-      <c r="AJ52" s="69">
+      <c r="AJ52" s="65">
         <f t="shared" si="11"/>
         <v>0.18865090699938322</v>
       </c>
-      <c r="AK52" s="69">
+      <c r="AK52" s="126">
         <f t="shared" si="11"/>
         <v>0.20053719230054018</v>
       </c>
-      <c r="AL52" s="69">
+      <c r="AL52" s="65">
         <f t="shared" si="11"/>
         <v>0.19313555433892682</v>
       </c>
-      <c r="AM52" s="69">
+      <c r="AM52" s="65">
         <f t="shared" si="11"/>
         <v>0.19775029848561318</v>
       </c>
-      <c r="AN52" s="69">
+      <c r="AN52" s="126">
         <f t="shared" si="11"/>
         <v>0.19544292641226998</v>
       </c>
-      <c r="AO52" s="69">
+      <c r="AO52" s="65">
         <f t="shared" si="11"/>
         <v>0.19738571671796856</v>
       </c>
-      <c r="AP52" s="69">
+      <c r="AP52" s="65">
         <f t="shared" si="11"/>
         <v>0.19678547687735395</v>
       </c>
-      <c r="AQ52" s="69">
+      <c r="AQ52" s="126">
         <f t="shared" si="11"/>
         <v>0.19708559679766124</v>
       </c>
-      <c r="AR52" s="69">
+      <c r="AR52" s="65">
         <f t="shared" si="11"/>
         <v>0.20412512617462275</v>
       </c>
-      <c r="AS52" s="69">
+      <c r="AS52" s="65">
         <f t="shared" si="11"/>
         <v>0.20588494332962287</v>
       </c>
-      <c r="AT52" s="69">
+      <c r="AT52" s="126">
         <f t="shared" si="11"/>
         <v>0.20500503475212281</v>
       </c>
-      <c r="AU52" s="69">
+      <c r="AU52" s="65">
         <f t="shared" si="11"/>
         <v>0.20520260295952247</v>
       </c>
-      <c r="AV52" s="69">
+      <c r="AV52" s="65">
         <f t="shared" si="11"/>
         <v>0.20721900262116216</v>
       </c>
-      <c r="AW52" s="69">
+      <c r="AW52" s="126">
         <f t="shared" si="11"/>
         <v>0.20621080279034229</v>
       </c>
-      <c r="AX52" s="69">
+      <c r="AX52" s="65">
         <f t="shared" si="11"/>
         <v>0.20969142014588582</v>
       </c>
-      <c r="AY52" s="69">
+      <c r="AY52" s="65">
         <f t="shared" si="11"/>
         <v>0.21282906347200575</v>
       </c>
-      <c r="AZ52" s="69">
+      <c r="AZ52" s="126">
         <f t="shared" si="11"/>
         <v>0.21126024180894573</v>
       </c>
@@ -6237,53 +7660,53 @@
         <v>48</v>
       </c>
       <c r="AI53" s="15"/>
-      <c r="AJ53" s="57"/>
-      <c r="AK53" s="57"/>
+      <c r="AJ53" s="56"/>
+      <c r="AK53" s="127"/>
       <c r="AL53" s="51">
         <f>+AL52</f>
         <v>0.19313555433892682</v>
       </c>
-      <c r="AM53" s="54">
+      <c r="AM53" s="53">
         <f>+AM52</f>
         <v>0.19775029848561318</v>
       </c>
-      <c r="AN53" s="52"/>
-      <c r="AO53" s="54">
+      <c r="AN53" s="139"/>
+      <c r="AO53" s="53">
         <f>+AO52</f>
         <v>0.19738571671796856</v>
       </c>
-      <c r="AP53" s="54">
+      <c r="AP53" s="53">
         <f>+AP52</f>
         <v>0.19678547687735395</v>
       </c>
-      <c r="AQ53" s="52"/>
-      <c r="AR53" s="54">
+      <c r="AQ53" s="139"/>
+      <c r="AR53" s="53">
         <f>+AR52</f>
         <v>0.20412512617462275</v>
       </c>
-      <c r="AS53" s="74">
+      <c r="AS53" s="70">
         <f>+AS52</f>
         <v>0.20588494332962287</v>
       </c>
-      <c r="AT53" s="57"/>
-      <c r="AU53" s="56">
+      <c r="AT53" s="127"/>
+      <c r="AU53" s="55">
         <f>+AU52</f>
         <v>0.20520260295952247</v>
       </c>
-      <c r="AV53" s="56">
+      <c r="AV53" s="55">
         <f>+AV52</f>
         <v>0.20721900262116216</v>
       </c>
-      <c r="AW53" s="57"/>
-      <c r="AX53" s="56">
+      <c r="AW53" s="127"/>
+      <c r="AX53" s="55">
         <f>+AX52</f>
         <v>0.20969142014588582</v>
       </c>
-      <c r="AY53" s="56">
+      <c r="AY53" s="55">
         <f>+AY52</f>
         <v>0.21282906347200575</v>
       </c>
-      <c r="AZ53" s="57"/>
+      <c r="AZ53" s="127"/>
     </row>
     <row r="54" spans="1:55" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A54" t="str">
@@ -6291,65 +7714,65 @@
         <v xml:space="preserve">                                                 second Q in sem</v>
       </c>
       <c r="AI54" s="15"/>
-      <c r="AJ54" s="57"/>
-      <c r="AK54" s="57"/>
-      <c r="AL54" s="58">
+      <c r="AJ54" s="56"/>
+      <c r="AK54" s="127"/>
+      <c r="AL54" s="57">
         <f>+AL52</f>
         <v>0.19313555433892682</v>
       </c>
-      <c r="AM54" s="61">
+      <c r="AM54" s="59">
         <f>+AM52</f>
         <v>0.19775029848561318</v>
       </c>
-      <c r="AN54" s="60" t="str">
+      <c r="AN54" s="124" t="str">
         <f>IF(ABS(AVERAGE(AL53:AM54)-AN52)&gt;0.1,"check","")</f>
         <v/>
       </c>
-      <c r="AO54" s="61">
+      <c r="AO54" s="59">
         <f>+AO52</f>
         <v>0.19738571671796856</v>
       </c>
-      <c r="AP54" s="61">
+      <c r="AP54" s="59">
         <f>+AP52</f>
         <v>0.19678547687735395</v>
       </c>
-      <c r="AQ54" s="60" t="str">
+      <c r="AQ54" s="124" t="str">
         <f>IF(ABS(AVERAGE(AO53:AP54)-AQ52)&gt;0.1,"check","")</f>
         <v/>
       </c>
-      <c r="AR54" s="61">
+      <c r="AR54" s="59">
         <f>+AR52</f>
         <v>0.20412512617462275</v>
       </c>
-      <c r="AS54" s="75">
+      <c r="AS54" s="71">
         <f>+AS52</f>
         <v>0.20588494332962287</v>
       </c>
-      <c r="AT54" s="99" t="str">
+      <c r="AT54" s="128" t="str">
         <f>IF(ABS(AVERAGE(AR53:AS54)-AT52)&gt;0.1,"check","")</f>
         <v/>
       </c>
-      <c r="AU54" s="56">
+      <c r="AU54" s="55">
         <f>+AU52</f>
         <v>0.20520260295952247</v>
       </c>
-      <c r="AV54" s="56">
+      <c r="AV54" s="55">
         <f>+AV52</f>
         <v>0.20721900262116216</v>
       </c>
-      <c r="AW54" s="98" t="str">
+      <c r="AW54" s="130" t="str">
         <f>IF(ABS(AVERAGE(AU53:AV54)-AW52)&gt;0.1,"check","")</f>
         <v/>
       </c>
-      <c r="AX54" s="56">
+      <c r="AX54" s="55">
         <f>+AX52</f>
         <v>0.20969142014588582</v>
       </c>
-      <c r="AY54" s="56">
+      <c r="AY54" s="55">
         <f>+AY52</f>
         <v>0.21282906347200575</v>
       </c>
-      <c r="AZ54" s="98" t="str">
+      <c r="AZ54" s="130" t="str">
         <f>IF(ABS(AVERAGE(AX53:AY54)-AZ52)&gt;0.1,"check","")</f>
         <v/>
       </c>
@@ -6357,25 +7780,25 @@
     <row r="55" spans="1:55" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
       <c r="AI55" s="15"/>
       <c r="AJ55" s="15"/>
-      <c r="AK55" s="15"/>
+      <c r="AK55" s="114"/>
       <c r="AL55" s="15"/>
       <c r="AM55" s="15"/>
-      <c r="AN55" s="15"/>
+      <c r="AN55" s="114"/>
       <c r="AO55" s="15"/>
       <c r="AP55" s="15"/>
-      <c r="AQ55" s="15"/>
+      <c r="AQ55" s="114"/>
       <c r="AR55" s="15"/>
       <c r="AS55" s="15"/>
-      <c r="AT55" s="15"/>
+      <c r="AT55" s="114"/>
       <c r="AU55" s="15"/>
       <c r="AV55" s="15"/>
-      <c r="AW55" s="15"/>
+      <c r="AW55" s="114"/>
       <c r="AX55" s="15"/>
       <c r="AY55" s="15"/>
-      <c r="AZ55" s="15"/>
+      <c r="AZ55" s="114"/>
     </row>
     <row r="56" spans="1:55" x14ac:dyDescent="0.75">
-      <c r="A56" s="65" t="str">
+      <c r="A56" s="61" t="str">
         <f>+A30</f>
         <v>Other Expenditure of %GDP</v>
       </c>
@@ -6387,7 +7810,7 @@
         <f t="shared" si="12"/>
         <v>4.595330829542054E-2</v>
       </c>
-      <c r="AK56" s="15">
+      <c r="AK56" s="114">
         <f t="shared" si="12"/>
         <v>4.8267929014096267E-2</v>
       </c>
@@ -6399,7 +7822,7 @@
         <f t="shared" si="12"/>
         <v>6.8464021255010693E-2</v>
       </c>
-      <c r="AN56" s="15">
+      <c r="AN56" s="114">
         <f t="shared" si="12"/>
         <v>6.5305740908504314E-2</v>
       </c>
@@ -6411,7 +7834,7 @@
         <f t="shared" si="12"/>
         <v>5.7522104816690109E-2</v>
       </c>
-      <c r="AQ56" s="15">
+      <c r="AQ56" s="114">
         <f t="shared" si="12"/>
         <v>5.7506975131284256E-2</v>
       </c>
@@ -6423,7 +7846,7 @@
         <f t="shared" si="12"/>
         <v>4.4717671027401498E-2</v>
       </c>
-      <c r="AT56" s="15">
+      <c r="AT56" s="114">
         <f t="shared" si="12"/>
         <v>4.8938235172937043E-2</v>
       </c>
@@ -6435,7 +7858,7 @@
         <f t="shared" si="12"/>
         <v>3.5500987718633741E-2</v>
       </c>
-      <c r="AW56" s="15">
+      <c r="AW56" s="114">
         <f t="shared" si="12"/>
         <v>3.5534903705779032E-2</v>
       </c>
@@ -6447,163 +7870,163 @@
         <f t="shared" si="12"/>
         <v>3.1001519033258772E-2</v>
       </c>
-      <c r="AZ56" s="15">
+      <c r="AZ56" s="114">
         <f t="shared" si="12"/>
         <v>3.2074422687699104E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:55" s="70" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A57" s="70" t="s">
+    <row r="57" spans="1:55" s="66" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A57" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="AF57" s="71"/>
-      <c r="AG57" s="71"/>
-      <c r="AH57" s="71"/>
-      <c r="AI57" s="71">
+      <c r="AF57" s="67"/>
+      <c r="AG57" s="67"/>
+      <c r="AH57" s="67"/>
+      <c r="AI57" s="67">
         <f>+AI69</f>
         <v>0</v>
       </c>
-      <c r="AJ57" s="71"/>
-      <c r="AK57" s="72">
+      <c r="AJ57" s="67"/>
+      <c r="AK57" s="129">
         <f t="shared" ref="AK57" si="13">+AK69</f>
         <v>3.5550430472671372E-3</v>
       </c>
-      <c r="AL57" s="72">
+      <c r="AL57" s="68">
         <f t="shared" ref="AL57:AZ57" si="14">+AL69</f>
         <v>3.7277171331734922E-2</v>
       </c>
-      <c r="AM57" s="72">
+      <c r="AM57" s="68">
         <f t="shared" si="14"/>
         <v>5.4785913549554137E-2</v>
       </c>
-      <c r="AN57" s="72">
+      <c r="AN57" s="129">
         <f t="shared" si="14"/>
         <v>4.6031542440644529E-2</v>
       </c>
-      <c r="AO57" s="72">
+      <c r="AO57" s="68">
         <f t="shared" si="14"/>
         <v>3.3923685167178079E-2</v>
       </c>
-      <c r="AP57" s="72">
+      <c r="AP57" s="68">
         <f t="shared" si="14"/>
         <v>3.9198390972127059E-2</v>
       </c>
-      <c r="AQ57" s="72">
+      <c r="AQ57" s="129">
         <f t="shared" si="14"/>
         <v>3.6561038069652572E-2</v>
       </c>
-      <c r="AR57" s="72">
+      <c r="AR57" s="68">
         <f t="shared" si="14"/>
         <v>3.3391888487969368E-2</v>
       </c>
-      <c r="AS57" s="72">
+      <c r="AS57" s="68">
         <f t="shared" si="14"/>
         <v>1.8962175027440388E-2</v>
       </c>
-      <c r="AT57" s="72">
+      <c r="AT57" s="129">
         <f t="shared" si="14"/>
         <v>2.6177031757704878E-2</v>
       </c>
-      <c r="AU57" s="72">
+      <c r="AU57" s="68">
         <f t="shared" si="14"/>
         <v>2.4223295422375626E-3</v>
       </c>
-      <c r="AV57" s="72">
+      <c r="AV57" s="68">
         <f t="shared" si="14"/>
         <v>2.4282105743104322E-3</v>
       </c>
-      <c r="AW57" s="72">
+      <c r="AW57" s="129">
         <f t="shared" si="14"/>
         <v>2.4252700582739974E-3</v>
       </c>
-      <c r="AX57" s="72">
+      <c r="AX57" s="68">
         <f t="shared" si="14"/>
         <v>1.9440881185176268E-3</v>
       </c>
-      <c r="AY57" s="72">
+      <c r="AY57" s="68">
         <f t="shared" si="14"/>
         <v>2.0424927645828427E-3</v>
       </c>
-      <c r="AZ57" s="72">
+      <c r="AZ57" s="129">
         <f t="shared" si="14"/>
         <v>1.9932904415502347E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:55" s="67" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A58" s="67" t="str">
+    <row r="58" spans="1:55" s="63" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A58" s="63" t="str">
         <f>+A38</f>
         <v xml:space="preserve">correction </v>
       </c>
-      <c r="AF58" s="73"/>
-      <c r="AG58" s="73"/>
-      <c r="AH58" s="73"/>
-      <c r="AI58" s="68">
+      <c r="AF58" s="69"/>
+      <c r="AG58" s="69"/>
+      <c r="AH58" s="69"/>
+      <c r="AI58" s="64">
         <v>0</v>
       </c>
-      <c r="AJ58" s="68">
+      <c r="AJ58" s="64">
         <v>0</v>
       </c>
-      <c r="AK58" s="68">
+      <c r="AK58" s="95">
         <v>0</v>
       </c>
-      <c r="AL58" s="68">
+      <c r="AL58" s="64">
         <v>0</v>
       </c>
-      <c r="AM58" s="68">
+      <c r="AM58" s="64">
         <f>-AL58</f>
         <v>0</v>
       </c>
-      <c r="AN58" s="68">
+      <c r="AN58" s="95">
         <f>+AL58+AM58</f>
         <v>0</v>
       </c>
-      <c r="AO58" s="68">
+      <c r="AO58" s="64">
         <v>0</v>
       </c>
-      <c r="AP58" s="68">
+      <c r="AP58" s="64">
         <f>-AO58</f>
         <v>0</v>
       </c>
-      <c r="AQ58" s="68">
+      <c r="AQ58" s="95">
         <f>+AO58+AP58</f>
         <v>0</v>
       </c>
-      <c r="AR58" s="68">
+      <c r="AR58" s="64">
         <v>0</v>
       </c>
-      <c r="AS58" s="68">
+      <c r="AS58" s="64">
         <f>-AR58</f>
         <v>0</v>
       </c>
-      <c r="AT58" s="68">
+      <c r="AT58" s="95">
         <f>+AR58+AS58</f>
         <v>0</v>
       </c>
-      <c r="AU58" s="68">
+      <c r="AU58" s="64">
         <v>0</v>
       </c>
-      <c r="AV58" s="68">
+      <c r="AV58" s="64">
         <f>-AU58</f>
         <v>0</v>
       </c>
-      <c r="AW58" s="68">
+      <c r="AW58" s="95">
         <f>+AU58+AV58</f>
         <v>0</v>
       </c>
-      <c r="AX58" s="68">
+      <c r="AX58" s="64">
         <v>0</v>
       </c>
-      <c r="AY58" s="68">
+      <c r="AY58" s="64">
         <f>-AX58</f>
         <v>0</v>
       </c>
-      <c r="AZ58" s="68">
+      <c r="AZ58" s="95">
         <f>+AX58+AY58</f>
         <v>0</v>
       </c>
-      <c r="BA58" s="68"/>
-      <c r="BB58" s="68"/>
-      <c r="BC58" s="68"/>
+      <c r="BA58" s="64"/>
+      <c r="BB58" s="64"/>
+      <c r="BC58" s="64"/>
     </row>
     <row r="59" spans="1:55" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A59" s="49" t="s">
@@ -6617,7 +8040,7 @@
         <f t="shared" si="15"/>
         <v>4.595330829542054E-2</v>
       </c>
-      <c r="AK59" s="50">
+      <c r="AK59" s="121">
         <f t="shared" si="15"/>
         <v>4.8267929014096267E-2</v>
       </c>
@@ -6629,7 +8052,7 @@
         <f t="shared" ref="AM59:AQ59" si="16">+AM56+AM58</f>
         <v>6.8464021255010693E-2</v>
       </c>
-      <c r="AN59" s="50">
+      <c r="AN59" s="121">
         <f t="shared" si="16"/>
         <v>6.5305740908504314E-2</v>
       </c>
@@ -6641,7 +8064,7 @@
         <f t="shared" si="16"/>
         <v>5.7522104816690109E-2</v>
       </c>
-      <c r="AQ59" s="50">
+      <c r="AQ59" s="121">
         <f t="shared" si="16"/>
         <v>5.7506975131284256E-2</v>
       </c>
@@ -6653,7 +8076,7 @@
         <f t="shared" ref="AS59:AW59" si="17">+AS56+AS58</f>
         <v>4.4717671027401498E-2</v>
       </c>
-      <c r="AT59" s="50">
+      <c r="AT59" s="121">
         <f t="shared" si="17"/>
         <v>4.8938235172937043E-2</v>
       </c>
@@ -6665,7 +8088,7 @@
         <f t="shared" si="17"/>
         <v>3.5500987718633741E-2</v>
       </c>
-      <c r="AW59" s="50">
+      <c r="AW59" s="121">
         <f t="shared" si="17"/>
         <v>3.5534903705779032E-2</v>
       </c>
@@ -6677,7 +8100,7 @@
         <f t="shared" ref="AY59:AZ59" si="18">+AY56+AY58</f>
         <v>3.1001519033258772E-2</v>
       </c>
-      <c r="AZ59" s="50">
+      <c r="AZ59" s="121">
         <f t="shared" si="18"/>
         <v>3.2074422687699104E-2</v>
       </c>
@@ -6693,110 +8116,110 @@
         <f>+AL59</f>
         <v>6.2147460561997943E-2</v>
       </c>
-      <c r="AM60" s="54">
+      <c r="AM60" s="53">
         <f>+AM59</f>
         <v>6.8464021255010693E-2</v>
       </c>
-      <c r="AN60" s="52"/>
-      <c r="AO60" s="54">
+      <c r="AN60" s="139"/>
+      <c r="AO60" s="53">
         <f>+AO59</f>
         <v>5.749184544587839E-2</v>
       </c>
-      <c r="AP60" s="54">
+      <c r="AP60" s="53">
         <f>+AP59</f>
         <v>5.7522104816690109E-2</v>
       </c>
-      <c r="AQ60" s="52"/>
-      <c r="AR60" s="54">
+      <c r="AQ60" s="139"/>
+      <c r="AR60" s="53">
         <f>+AR59</f>
         <v>5.3158799318472595E-2</v>
       </c>
-      <c r="AS60" s="74">
+      <c r="AS60" s="70">
         <f>+AS59</f>
         <v>4.4717671027401498E-2</v>
       </c>
-      <c r="AT60" s="57"/>
-      <c r="AU60" s="56">
+      <c r="AT60" s="127"/>
+      <c r="AU60" s="55">
         <f>+AU59</f>
         <v>3.5568819692924324E-2</v>
       </c>
-      <c r="AV60" s="56">
+      <c r="AV60" s="55">
         <f>+AV59</f>
         <v>3.5500987718633741E-2</v>
       </c>
-      <c r="AW60" s="57"/>
-      <c r="AX60" s="56">
+      <c r="AW60" s="127"/>
+      <c r="AX60" s="55">
         <f>+AX59</f>
         <v>3.3147326342139447E-2</v>
       </c>
-      <c r="AY60" s="56">
+      <c r="AY60" s="55">
         <f>+AY59</f>
         <v>3.1001519033258772E-2</v>
       </c>
-      <c r="AZ60" s="57"/>
+      <c r="AZ60" s="127"/>
     </row>
     <row r="61" spans="1:55" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A61" t="str">
         <f>+A54</f>
         <v xml:space="preserve">                                                 second Q in sem</v>
       </c>
-      <c r="AL61" s="58">
+      <c r="AL61" s="57">
         <f>+AL59</f>
         <v>6.2147460561997943E-2</v>
       </c>
-      <c r="AM61" s="61">
+      <c r="AM61" s="59">
         <f>+AM59</f>
         <v>6.8464021255010693E-2</v>
       </c>
-      <c r="AN61" s="60" t="str">
+      <c r="AN61" s="124" t="str">
         <f>IF(ABS(AVERAGE(AL60:AM61)-AN59)&gt;0.001,"check","")</f>
         <v/>
       </c>
-      <c r="AO61" s="61">
+      <c r="AO61" s="59">
         <f>+AO59</f>
         <v>5.749184544587839E-2</v>
       </c>
-      <c r="AP61" s="61">
+      <c r="AP61" s="59">
         <f>+AP59</f>
         <v>5.7522104816690109E-2</v>
       </c>
-      <c r="AQ61" s="60" t="str">
+      <c r="AQ61" s="124" t="str">
         <f>IF(ABS(AVERAGE(AO60:AP61)-AQ59)&gt;0.001,"check","")</f>
         <v/>
       </c>
-      <c r="AR61" s="61">
+      <c r="AR61" s="59">
         <f>+AR59</f>
         <v>5.3158799318472595E-2</v>
       </c>
-      <c r="AS61" s="75">
+      <c r="AS61" s="71">
         <f>+AS59</f>
         <v>4.4717671027401498E-2</v>
       </c>
-      <c r="AT61" s="98" t="str">
+      <c r="AT61" s="130" t="str">
         <f>IF(ABS(AVERAGE(AR60:AS61)-AT59)&gt;0.001,"check","")</f>
         <v/>
       </c>
-      <c r="AU61" s="56">
+      <c r="AU61" s="55">
         <f>+AU59</f>
         <v>3.5568819692924324E-2</v>
       </c>
-      <c r="AV61" s="56">
+      <c r="AV61" s="55">
         <f>+AV59</f>
         <v>3.5500987718633741E-2</v>
       </c>
-      <c r="AW61" s="98" t="str">
+      <c r="AW61" s="130" t="str">
         <f>IF(ABS(AVERAGE(AU60:AV61)-AW59)&gt;0.001,"check","")</f>
         <v/>
       </c>
-      <c r="AX61" s="56">
+      <c r="AX61" s="55">
         <f>+AX59</f>
         <v>3.3147326342139447E-2</v>
       </c>
-      <c r="AY61" s="56">
+      <c r="AY61" s="55">
         <f>+AY59</f>
         <v>3.1001519033258772E-2</v>
       </c>
-      <c r="AZ61" s="98" t="str">
+      <c r="AZ61" s="130" t="str">
         <f>IF(ABS(AVERAGE(AX60:AY61)-AZ59)&gt;0.001,"check","")</f>
         <v/>
       </c>
@@ -6805,178 +8228,178 @@
       <c r="A62" t="s">
         <v>63</v>
       </c>
-      <c r="AN62" s="47">
+      <c r="AN62" s="78">
         <f>+AN59-AN57</f>
         <v>1.9274198467859785E-2</v>
       </c>
-      <c r="AQ62" s="47">
+      <c r="AQ62" s="78">
         <f>+AQ59-AQ57</f>
         <v>2.0945937061631684E-2</v>
       </c>
-      <c r="AT62" s="47">
+      <c r="AT62" s="78">
         <f>+AT59-AT57</f>
         <v>2.2761203415232165E-2</v>
       </c>
-      <c r="AW62" s="47">
+      <c r="AW62" s="78">
         <f>+AW59-AW57</f>
         <v>3.3109633647505035E-2</v>
       </c>
-      <c r="AZ62" s="47">
+      <c r="AZ62" s="78">
         <f>+AZ59-AZ57</f>
         <v>3.0081132246148869E-2</v>
       </c>
     </row>
     <row r="64" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A64" s="76" t="s">
+      <c r="A64" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="AI64" s="77" t="str">
+      <c r="AI64" s="73" t="str">
         <f t="shared" ref="AI64:AK64" si="19">+IF(ABS(AI43-AI50-AI56-AI37)&gt;0.1,"check","")</f>
         <v/>
       </c>
-      <c r="AJ64" s="78" t="str">
+      <c r="AJ64" s="74" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AK64" s="78" t="str">
+      <c r="AK64" s="131" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AL64" s="78" t="str">
+      <c r="AL64" s="74" t="str">
         <f>+IF(ABS(AL43-AL50-AL56-AL37)&gt;0.1,"check","")</f>
         <v/>
       </c>
-      <c r="AM64" s="78" t="str">
+      <c r="AM64" s="74" t="str">
         <f t="shared" ref="AM64:AZ64" si="20">+IF(ABS(AM43-AM50-AM56-AM37)&gt;0.1,"check","")</f>
         <v/>
       </c>
-      <c r="AN64" s="78" t="str">
+      <c r="AN64" s="131" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AO64" s="78" t="str">
+      <c r="AO64" s="74" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AP64" s="78" t="str">
+      <c r="AP64" s="74" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AQ64" s="78" t="str">
+      <c r="AQ64" s="131" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AR64" s="78" t="str">
+      <c r="AR64" s="74" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AS64" s="78" t="str">
+      <c r="AS64" s="74" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AT64" s="78" t="str">
+      <c r="AT64" s="131" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AU64" s="78" t="str">
+      <c r="AU64" s="74" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AV64" s="78" t="str">
+      <c r="AV64" s="74" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW64" s="78" t="str">
+      <c r="AW64" s="131" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AX64" s="78" t="str">
+      <c r="AX64" s="74" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AY64" s="78" t="str">
+      <c r="AY64" s="74" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AZ64" s="78" t="str">
+      <c r="AZ64" s="131" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="65" spans="1:53" x14ac:dyDescent="0.75">
-      <c r="A65" s="76" t="str">
+      <c r="A65" s="72" t="str">
         <f>+A64</f>
         <v>check</v>
       </c>
-      <c r="AI65" s="79" t="str">
+      <c r="AI65" s="75" t="str">
         <f t="shared" ref="AI65:AK65" si="21">+IF(ABS(AI43-AI52-AI59-AI39)&gt;0.1,"check","")</f>
         <v/>
       </c>
-      <c r="AJ65" s="80" t="str">
+      <c r="AJ65" s="76" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AK65" s="80" t="str">
+      <c r="AK65" s="132" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AL65" s="80" t="str">
+      <c r="AL65" s="76" t="str">
         <f>+IF(ABS(AL43-AL52-AL59-AL39)&gt;0.1,"check","")</f>
         <v/>
       </c>
-      <c r="AM65" s="80" t="str">
+      <c r="AM65" s="76" t="str">
         <f t="shared" ref="AM65:AZ65" si="22">+IF(ABS(AM43-AM52-AM59-AM39)&gt;0.1,"check","")</f>
         <v/>
       </c>
-      <c r="AN65" s="80" t="str">
+      <c r="AN65" s="132" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AO65" s="80" t="str">
+      <c r="AO65" s="76" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AP65" s="80" t="str">
+      <c r="AP65" s="76" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AQ65" s="80" t="str">
+      <c r="AQ65" s="132" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AR65" s="80" t="str">
+      <c r="AR65" s="76" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AS65" s="80" t="str">
+      <c r="AS65" s="76" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AT65" s="80" t="str">
+      <c r="AT65" s="132" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AU65" s="80" t="str">
+      <c r="AU65" s="76" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV65" s="80" t="str">
+      <c r="AV65" s="76" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AW65" s="80" t="str">
+      <c r="AW65" s="132" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AX65" s="80" t="str">
+      <c r="AX65" s="76" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AY65" s="80" t="str">
+      <c r="AY65" s="76" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AZ65" s="80" t="str">
+      <c r="AZ65" s="132" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -6985,10 +8408,10 @@
       </c>
     </row>
     <row r="66" spans="1:53" x14ac:dyDescent="0.75">
-      <c r="AI66" s="92" t="s">
+      <c r="AI66" s="88" t="s">
         <v>52</v>
       </c>
-      <c r="AJ66" s="93" t="s">
+      <c r="AJ66" s="89" t="s">
         <v>61</v>
       </c>
     </row>
@@ -6996,77 +8419,77 @@
       <c r="A67" t="s">
         <v>76</v>
       </c>
-      <c r="AI67" s="94" t="s">
+      <c r="AI67" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="AJ67" s="95">
+      <c r="AJ67" s="91">
         <v>840.56</v>
       </c>
-      <c r="AK67" s="81">
+      <c r="AK67" s="133">
         <f>+AK21</f>
         <v>36.150092620999999</v>
       </c>
-      <c r="AL67" s="81">
+      <c r="AL67" s="77">
         <f>+AL21</f>
         <v>215.09287778667468</v>
       </c>
-      <c r="AM67" s="81">
+      <c r="AM67" s="77">
         <f t="shared" ref="AM67:AZ67" si="23">+AM21</f>
         <v>316.12001089561022</v>
       </c>
-      <c r="AN67" s="81">
+      <c r="AN67" s="133">
         <f t="shared" si="23"/>
         <v>531.21288868228487</v>
       </c>
-      <c r="AO67" s="81">
+      <c r="AO67" s="77">
         <f t="shared" si="23"/>
         <v>222.02911425810541</v>
       </c>
-      <c r="AP67" s="81">
+      <c r="AP67" s="77">
         <f t="shared" si="23"/>
         <v>256.55184526664607</v>
       </c>
-      <c r="AQ67" s="81">
+      <c r="AQ67" s="133">
         <f t="shared" si="23"/>
         <v>478.58095952475151</v>
       </c>
-      <c r="AR67" s="81">
+      <c r="AR67" s="77">
         <f t="shared" si="23"/>
         <v>245.81139606098327</v>
       </c>
-      <c r="AS67" s="81">
+      <c r="AS67" s="77">
         <f t="shared" si="23"/>
         <v>139.58835294766789</v>
       </c>
-      <c r="AT67" s="81">
+      <c r="AT67" s="133">
         <f t="shared" si="23"/>
         <v>385.39974900865116</v>
       </c>
-      <c r="AU67" s="81">
+      <c r="AU67" s="77">
         <f t="shared" si="23"/>
         <v>19.988717131596964</v>
       </c>
-      <c r="AV67" s="81">
+      <c r="AV67" s="77">
         <f t="shared" si="23"/>
         <v>20.037246567619881</v>
       </c>
-      <c r="AW67" s="81">
+      <c r="AW67" s="133">
         <f t="shared" si="23"/>
         <v>40.025963699216845</v>
       </c>
-      <c r="AX67" s="81">
+      <c r="AX67" s="77">
         <f t="shared" si="23"/>
         <v>17.990922015319999</v>
       </c>
-      <c r="AY67" s="81">
+      <c r="AY67" s="77">
         <f t="shared" si="23"/>
         <v>18.901575342420418</v>
       </c>
-      <c r="AZ67" s="81">
+      <c r="AZ67" s="133">
         <f t="shared" si="23"/>
         <v>36.892497357740417</v>
       </c>
-      <c r="BA67" s="91">
+      <c r="BA67" s="87">
         <f>+AK67+AN67+AQ67+AT67+AW67+AZ67</f>
         <v>1508.262150893645</v>
       </c>
@@ -7075,152 +8498,152 @@
       <c r="A68" t="s">
         <v>79</v>
       </c>
-      <c r="AI68" s="79"/>
-      <c r="AJ68" s="96">
+      <c r="AI68" s="75"/>
+      <c r="AJ68" s="92">
         <v>1114.0999999999999</v>
       </c>
-      <c r="AK68" s="81">
+      <c r="AK68" s="133">
         <f t="shared" ref="AK68:AM68" si="24">+(AK67/$BA67)*$BA68</f>
         <v>40.325993411810664</v>
       </c>
-      <c r="AL68" s="81">
+      <c r="AL68" s="77">
         <f t="shared" si="24"/>
         <v>239.93946747218322</v>
       </c>
-      <c r="AM68" s="81">
+      <c r="AM68" s="77">
         <f t="shared" si="24"/>
         <v>352.63681369691767</v>
       </c>
-      <c r="AN68" s="81">
+      <c r="AN68" s="133">
         <f>+(AN67/$BA67)*$BA68</f>
         <v>592.57628116910087</v>
       </c>
-      <c r="AO68" s="81">
+      <c r="AO68" s="77">
         <f t="shared" ref="AO68:AZ68" si="25">+(AO67/$BA67)*$BA68</f>
         <v>247.67694768232215</v>
       </c>
-      <c r="AP68" s="81">
+      <c r="AP68" s="77">
         <f t="shared" si="25"/>
         <v>286.18759377675008</v>
       </c>
-      <c r="AQ68" s="81">
+      <c r="AQ68" s="133">
         <f t="shared" si="25"/>
         <v>533.86454145907226</v>
       </c>
-      <c r="AR68" s="81">
+      <c r="AR68" s="77">
         <f t="shared" si="25"/>
         <v>274.20645479466515</v>
       </c>
-      <c r="AS68" s="81">
+      <c r="AS68" s="77">
         <f t="shared" si="25"/>
         <v>155.71298973832185</v>
       </c>
-      <c r="AT68" s="81">
+      <c r="AT68" s="133">
         <f t="shared" si="25"/>
         <v>429.91944453298703</v>
       </c>
-      <c r="AU68" s="81">
+      <c r="AU68" s="77">
         <f t="shared" si="25"/>
         <v>22.297726421067978</v>
       </c>
-      <c r="AV68" s="81">
+      <c r="AV68" s="77">
         <f t="shared" si="25"/>
         <v>22.351861765556755</v>
       </c>
-      <c r="AW68" s="81">
+      <c r="AW68" s="133">
         <f t="shared" si="25"/>
         <v>44.649588186624733</v>
       </c>
-      <c r="AX68" s="81">
+      <c r="AX68" s="77">
         <f t="shared" si="25"/>
         <v>20.069154739613076</v>
       </c>
-      <c r="AY68" s="81">
+      <c r="AY68" s="77">
         <f t="shared" si="25"/>
         <v>21.08500276119635</v>
       </c>
-      <c r="AZ68" s="81">
+      <c r="AZ68" s="133">
         <f t="shared" si="25"/>
         <v>41.154157500809426</v>
       </c>
-      <c r="BA68" s="91">
+      <c r="BA68" s="87">
         <f>+'NKIA Financing'!H11</f>
         <v>1682.4900062604052</v>
       </c>
     </row>
-    <row r="69" spans="1:53" s="70" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A69" s="70" t="s">
+    <row r="69" spans="1:53" s="66" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A69" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="AF69" s="71"/>
-      <c r="AG69" s="71"/>
-      <c r="AH69" s="71"/>
-      <c r="AI69" s="71"/>
-      <c r="AJ69" s="112">
+      <c r="AF69" s="67"/>
+      <c r="AG69" s="67"/>
+      <c r="AH69" s="67"/>
+      <c r="AI69" s="67"/>
+      <c r="AJ69" s="104">
         <f>+AJ68/AJ67</f>
         <v>1.3254259065384981</v>
       </c>
-      <c r="AK69" s="72">
+      <c r="AK69" s="129">
         <f t="shared" ref="AK69:AZ69" si="26">+(AK67+AK68)/AK27</f>
         <v>3.5550430472671372E-3</v>
       </c>
-      <c r="AL69" s="116">
+      <c r="AL69" s="108">
         <f t="shared" si="26"/>
         <v>3.7277171331734922E-2</v>
       </c>
-      <c r="AM69" s="116">
+      <c r="AM69" s="108">
         <f t="shared" si="26"/>
         <v>5.4785913549554137E-2</v>
       </c>
-      <c r="AN69" s="72">
+      <c r="AN69" s="129">
         <f t="shared" si="26"/>
         <v>4.6031542440644529E-2</v>
       </c>
-      <c r="AO69" s="116">
+      <c r="AO69" s="108">
         <f t="shared" si="26"/>
         <v>3.3923685167178079E-2</v>
       </c>
-      <c r="AP69" s="116">
+      <c r="AP69" s="108">
         <f t="shared" si="26"/>
         <v>3.9198390972127059E-2</v>
       </c>
-      <c r="AQ69" s="72">
+      <c r="AQ69" s="129">
         <f t="shared" si="26"/>
         <v>3.6561038069652572E-2</v>
       </c>
-      <c r="AR69" s="116">
+      <c r="AR69" s="108">
         <f t="shared" si="26"/>
         <v>3.3391888487969368E-2</v>
       </c>
-      <c r="AS69" s="116">
+      <c r="AS69" s="108">
         <f t="shared" si="26"/>
         <v>1.8962175027440388E-2</v>
       </c>
-      <c r="AT69" s="72">
+      <c r="AT69" s="129">
         <f t="shared" si="26"/>
         <v>2.6177031757704878E-2</v>
       </c>
-      <c r="AU69" s="116">
+      <c r="AU69" s="108">
         <f t="shared" si="26"/>
         <v>2.4223295422375626E-3</v>
       </c>
-      <c r="AV69" s="116">
+      <c r="AV69" s="108">
         <f t="shared" si="26"/>
         <v>2.4282105743104322E-3</v>
       </c>
-      <c r="AW69" s="72">
+      <c r="AW69" s="129">
         <f t="shared" si="26"/>
         <v>2.4252700582739974E-3</v>
       </c>
-      <c r="AX69" s="116">
+      <c r="AX69" s="108">
         <f t="shared" si="26"/>
         <v>1.9440881185176268E-3</v>
       </c>
-      <c r="AY69" s="116">
+      <c r="AY69" s="108">
         <f t="shared" si="26"/>
         <v>2.0424927645828427E-3</v>
       </c>
-      <c r="AZ69" s="72">
+      <c r="AZ69" s="129">
         <f t="shared" si="26"/>
         <v>1.9932904415502347E-3</v>
       </c>
@@ -7253,15 +8676,15 @@
       <c r="AR71" s="44"/>
     </row>
     <row r="72" spans="1:53" x14ac:dyDescent="0.75">
-      <c r="AJ72" s="90" t="s">
+      <c r="AJ72" s="86" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="73" spans="1:53" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="A73" s="65" t="s">
+      <c r="A73" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="AJ73" s="82">
+      <c r="AJ73" s="78">
         <f>+AVERAGE(AN73,AQ73)</f>
         <v>4.1296290255148554E-2</v>
       </c>
@@ -7273,7 +8696,7 @@
         <f t="shared" si="28"/>
         <v>5.4785913549554137E-2</v>
       </c>
-      <c r="AN73" s="82">
+      <c r="AN73" s="78">
         <f t="shared" ref="AN73:AT73" si="29">+AN57</f>
         <v>4.6031542440644529E-2</v>
       </c>
@@ -7285,7 +8708,7 @@
         <f t="shared" si="29"/>
         <v>3.9198390972127059E-2</v>
       </c>
-      <c r="AQ73" s="82">
+      <c r="AQ73" s="78">
         <f t="shared" si="29"/>
         <v>3.6561038069652572E-2</v>
       </c>
@@ -7297,433 +8720,863 @@
         <f t="shared" si="29"/>
         <v>1.8962175027440388E-2</v>
       </c>
-      <c r="AT73" s="82">
+      <c r="AT73" s="78">
         <f t="shared" si="29"/>
         <v>2.6177031757704878E-2</v>
       </c>
       <c r="AU73" s="47"/>
       <c r="AV73" s="47"/>
-      <c r="AW73" s="47"/>
+      <c r="AW73" s="78"/>
       <c r="AY73" s="47"/>
-      <c r="AZ73" s="47"/>
+      <c r="AZ73" s="78"/>
     </row>
     <row r="74" spans="1:53" ht="15.5" thickTop="1" x14ac:dyDescent="0.75">
-      <c r="A74" s="70" t="s">
+      <c r="A74" s="66" t="s">
         <v>54</v>
       </c>
       <c r="AJ74" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="AL74" s="83">
+      <c r="AL74" s="79">
         <f>+$AJ$73/$AJ$75*$AJ$78*AL77</f>
         <v>4.4737647776410934E-2</v>
       </c>
-      <c r="AM74" s="84">
+      <c r="AM74" s="80">
         <f>+$AJ$73/$AJ$75*$AJ$78*AM77</f>
         <v>7.9151222989034722E-2</v>
       </c>
-      <c r="AN74" s="52"/>
-      <c r="AO74" s="84">
+      <c r="AN74" s="139"/>
+      <c r="AO74" s="80">
         <f>+$AJ$73/$AJ$75*$AJ$78*AO77</f>
         <v>8.9475295552821868E-2</v>
       </c>
-      <c r="AP74" s="84">
+      <c r="AP74" s="80">
         <f>+$AJ$73/$AJ$75*$AJ$78*AP77</f>
         <v>5.8503077861460452E-2</v>
       </c>
-      <c r="AQ74" s="102"/>
-      <c r="AR74" s="84">
+      <c r="AQ74" s="140"/>
+      <c r="AR74" s="80">
         <f>+$AT$73/$AJ$75*$AJ$78*AR77</f>
         <v>4.3628386262841462E-2</v>
       </c>
-      <c r="AS74" s="84">
+      <c r="AS74" s="80">
         <f>+$AT$73/$AJ$75*$AJ$78*AS77</f>
         <v>4.3628386262841462E-2</v>
       </c>
-      <c r="AT74" s="55"/>
+      <c r="AT74" s="134"/>
     </row>
     <row r="75" spans="1:53" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="A75" s="70" t="s">
+      <c r="A75" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="AJ75" s="87">
+      <c r="AJ75" s="83">
         <v>0.15</v>
       </c>
-      <c r="AL75" s="85">
+      <c r="AL75" s="81">
         <f>+$AJ$73/$AJ$75*$AJ$78*AL78</f>
         <v>5.8503077861460452E-2</v>
       </c>
-      <c r="AM75" s="86">
+      <c r="AM75" s="82">
         <f>+$AJ$73/$AJ$75*$AJ$78*AM78</f>
         <v>8.9475295552821868E-2</v>
       </c>
-      <c r="AN75" s="60">
+      <c r="AN75" s="124">
         <f>AVERAGE(AL74:AM76)</f>
         <v>6.7966811044931991E-2</v>
       </c>
-      <c r="AO75" s="86">
+      <c r="AO75" s="82">
         <f>+$AJ$73/$AJ$75*$AJ$78*AO78</f>
         <v>7.9151222989034722E-2</v>
       </c>
-      <c r="AP75" s="86">
+      <c r="AP75" s="82">
         <f>+$AJ$73/$AJ$75*$AJ$78*AP78</f>
         <v>4.4737647776410934E-2</v>
       </c>
-      <c r="AQ75" s="60">
+      <c r="AQ75" s="124">
         <f>AVERAGE(AO74:AP76)</f>
         <v>6.7966811044931991E-2</v>
       </c>
-      <c r="AR75" s="86">
+      <c r="AR75" s="82">
         <f t="shared" ref="AR75" si="30">+$AT$73/$AJ$75*$AJ$78*AR78</f>
         <v>4.3628386262841462E-2</v>
       </c>
-      <c r="AS75" s="86">
+      <c r="AS75" s="82">
         <f>+$AT$73/$AJ$75*$AJ$78*AS78</f>
         <v>4.3628386262841462E-2</v>
       </c>
-      <c r="AT75" s="60">
+      <c r="AT75" s="124">
         <f>AVERAGE(AR74:AS76)</f>
         <v>4.3628386262841462E-2</v>
       </c>
     </row>
     <row r="76" spans="1:53" ht="16.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="A76" s="70"/>
-      <c r="AJ76" s="87"/>
-      <c r="AN76" s="103"/>
+      <c r="A76" s="66"/>
+      <c r="AJ76" s="83"/>
+      <c r="AN76" s="141"/>
     </row>
     <row r="77" spans="1:53" x14ac:dyDescent="0.75">
-      <c r="AJ77" s="117" t="s">
+      <c r="AJ77" s="109" t="s">
         <v>58</v>
       </c>
-      <c r="AK77" s="45" t="s">
+      <c r="AK77" s="143" t="s">
         <v>57</v>
       </c>
-      <c r="AL77" s="88">
+      <c r="AL77" s="84">
         <v>0.65</v>
       </c>
-      <c r="AM77" s="88">
+      <c r="AM77" s="84">
         <v>1.1499999999999999</v>
       </c>
-      <c r="AO77" s="88">
+      <c r="AO77" s="84">
         <f>+AM78</f>
         <v>1.3</v>
       </c>
-      <c r="AP77" s="88">
+      <c r="AP77" s="84">
         <f>+AL78</f>
         <v>0.85</v>
       </c>
-      <c r="AR77" s="88">
+      <c r="AR77" s="84">
         <v>1</v>
       </c>
-      <c r="AS77" s="88">
+      <c r="AS77" s="84">
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:53" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="AJ78" s="118">
+      <c r="AJ78" s="110">
         <v>0.25</v>
       </c>
-      <c r="AL78" s="88">
+      <c r="AL78" s="84">
         <v>0.85</v>
       </c>
-      <c r="AM78" s="88">
+      <c r="AM78" s="84">
         <v>1.3</v>
       </c>
-      <c r="AO78" s="88">
+      <c r="AO78" s="84">
         <f>+AM77</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="AP78" s="88">
+      <c r="AP78" s="84">
         <f>+AL77</f>
         <v>0.65</v>
       </c>
-      <c r="AR78" s="88">
+      <c r="AR78" s="84">
         <v>1</v>
       </c>
-      <c r="AS78" s="88">
+      <c r="AS78" s="84">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:53" x14ac:dyDescent="0.75">
-      <c r="A79" s="89" t="s">
+      <c r="A79" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="AN79" s="88"/>
+      <c r="AN79" s="142"/>
+    </row>
+    <row r="81" spans="1:42" x14ac:dyDescent="0.75">
+      <c r="AE81" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG81" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH81" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI81" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ81" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK81" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL81" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM81" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN81" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO81" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP81" s="43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83" spans="1:42" x14ac:dyDescent="0.75">
+      <c r="A83" t="str">
+        <f>A28</f>
+        <v>Grev in % of GDP</v>
+      </c>
+      <c r="AE83" s="78">
+        <v>0.19014996739316092</v>
+      </c>
+      <c r="AF83" s="78">
+        <v>0.18314644640250893</v>
+      </c>
+      <c r="AG83" s="78">
+        <v>0.19117087620602016</v>
+      </c>
+      <c r="AH83" s="78">
+        <v>0.18431901010679033</v>
+      </c>
+      <c r="AI83" s="78">
+        <v>0.17014303403236622</v>
+      </c>
+      <c r="AJ83" s="78">
+        <v>0.16620417789665298</v>
+      </c>
+      <c r="AK83" s="78">
+        <v>0.16546014323811886</v>
+      </c>
+      <c r="AL83" s="78">
+        <f>AN28</f>
+        <v>0.17626652465618078</v>
+      </c>
+      <c r="AM83" s="78">
+        <f>AQ28</f>
+        <v>0.18383799968178346</v>
+      </c>
+      <c r="AN83" s="78">
+        <f>AT28</f>
+        <v>0.18786735635011592</v>
+      </c>
+      <c r="AO83" s="78">
+        <f>AW28</f>
+        <v>0.18985626615967205</v>
+      </c>
+      <c r="AP83" s="78">
+        <f>AZ28</f>
+        <v>0.19254613324113448</v>
+      </c>
+    </row>
+    <row r="84" spans="1:42" x14ac:dyDescent="0.75">
+      <c r="A84" t="str">
+        <f t="shared" ref="A84:A89" si="31">A29</f>
+        <v>Gdem in % of GDP</v>
+      </c>
+      <c r="AE84" s="78">
+        <v>0.26169584838513593</v>
+      </c>
+      <c r="AF84" s="78">
+        <v>0.26811145968691313</v>
+      </c>
+      <c r="AG84" s="78">
+        <v>0.27570065921784898</v>
+      </c>
+      <c r="AH84" s="78">
+        <v>0.28377582490937286</v>
+      </c>
+      <c r="AI84" s="78">
+        <v>0.24368260292576732</v>
+      </c>
+      <c r="AJ84" s="78">
+        <v>0.22612197687473534</v>
+      </c>
+      <c r="AK84" s="78">
+        <v>0.20053719230054018</v>
+      </c>
+      <c r="AL84" s="78">
+        <f t="shared" ref="AL84:AL85" si="32">AN29</f>
+        <v>0.19544292641226998</v>
+      </c>
+      <c r="AM84" s="78">
+        <f t="shared" ref="AM84:AM85" si="33">AQ29</f>
+        <v>0.19708559679766124</v>
+      </c>
+      <c r="AN84" s="78">
+        <f t="shared" ref="AN84:AN85" si="34">AT29</f>
+        <v>0.20500503475212281</v>
+      </c>
+      <c r="AO84" s="78">
+        <f t="shared" ref="AO84:AO85" si="35">AW29</f>
+        <v>0.20621080279034229</v>
+      </c>
+      <c r="AP84" s="78">
+        <f t="shared" ref="AP84:AP85" si="36">AZ29</f>
+        <v>0.21126024180894573</v>
+      </c>
+    </row>
+    <row r="85" spans="1:42" x14ac:dyDescent="0.75">
+      <c r="A85" t="str">
+        <f t="shared" si="31"/>
+        <v>Other Expenditure of %GDP</v>
+      </c>
+      <c r="AK85" s="78">
+        <f t="shared" ref="AK84:AK89" si="37">AK30</f>
+        <v>4.8267929014096267E-2</v>
+      </c>
+      <c r="AL85" s="78">
+        <f t="shared" si="32"/>
+        <v>6.5305740908504314E-2</v>
+      </c>
+      <c r="AM85" s="78">
+        <f t="shared" si="33"/>
+        <v>5.7506975131284256E-2</v>
+      </c>
+      <c r="AN85" s="78">
+        <f t="shared" si="34"/>
+        <v>4.8938235172937043E-2</v>
+      </c>
+      <c r="AO85" s="78">
+        <f t="shared" si="35"/>
+        <v>3.5534903705779032E-2</v>
+      </c>
+      <c r="AP85" s="78">
+        <f t="shared" si="36"/>
+        <v>3.2074422687699104E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:42" x14ac:dyDescent="0.75">
+      <c r="A86" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">    O/w Net Lending</v>
+      </c>
+      <c r="AK86" s="78">
+        <f t="shared" si="37"/>
+        <v>7.6216379010740978E-3</v>
+      </c>
+      <c r="AL86" s="78">
+        <f t="shared" ref="AL86:AL89" si="38">AN31</f>
+        <v>2.426235405315183E-2</v>
+      </c>
+      <c r="AM86" s="78">
+        <f t="shared" ref="AM86:AM89" si="39">AQ31</f>
+        <v>1.8456095568033321E-2</v>
+      </c>
+      <c r="AN86" s="78">
+        <f t="shared" ref="AN86:AN89" si="40">AT31</f>
+        <v>1.3338318225031951E-2</v>
+      </c>
+      <c r="AO86" s="78">
+        <f t="shared" ref="AO86:AO89" si="41">AW31</f>
+        <v>2.0068315060444027E-3</v>
+      </c>
+      <c r="AP86" s="78">
+        <f t="shared" ref="AP86:AP89" si="42">AZ31</f>
+        <v>1.6801053432437812E-3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:42" x14ac:dyDescent="0.75">
+      <c r="A87" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">    O/w Bugesera </v>
+      </c>
+      <c r="AK87" s="78">
+        <f t="shared" si="37"/>
+        <v>1.6804617246653031E-3</v>
+      </c>
+      <c r="AL87" s="78">
+        <f t="shared" si="38"/>
+        <v>2.1759017871323384E-2</v>
+      </c>
+      <c r="AM87" s="78">
+        <f t="shared" si="39"/>
+        <v>1.7282329432638625E-2</v>
+      </c>
+      <c r="AN87" s="78">
+        <f t="shared" si="40"/>
+        <v>1.2373830456986199E-2</v>
+      </c>
+      <c r="AO87" s="78">
+        <f t="shared" si="41"/>
+        <v>1.1464202966653949E-3</v>
+      </c>
+      <c r="AP87" s="78">
+        <f t="shared" si="42"/>
+        <v>9.4222439746301809E-4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:42" x14ac:dyDescent="0.75">
+      <c r="A88" t="str">
+        <f t="shared" si="31"/>
+        <v>Tot Spending in % of GDP</v>
+      </c>
+      <c r="AE88" s="78">
+        <v>0.27139661636466372</v>
+      </c>
+      <c r="AF88" s="78">
+        <v>0.29958819734316722</v>
+      </c>
+      <c r="AG88" s="78">
+        <v>0.32366045585195247</v>
+      </c>
+      <c r="AH88" s="78">
+        <v>0.33670696675965084</v>
+      </c>
+      <c r="AI88" s="78">
+        <v>0.35185267843523671</v>
+      </c>
+      <c r="AJ88" s="78">
+        <v>0.29533472921204673</v>
+      </c>
+      <c r="AK88" s="78">
+        <v>0.27432440534114733</v>
+      </c>
+      <c r="AL88" s="78">
+        <f t="shared" si="38"/>
+        <v>0.26074866732077423</v>
+      </c>
+      <c r="AM88" s="78">
+        <f t="shared" si="39"/>
+        <v>0.25459257192894552</v>
+      </c>
+      <c r="AN88" s="78">
+        <f t="shared" si="40"/>
+        <v>0.25394326992505989</v>
+      </c>
+      <c r="AO88" s="78">
+        <f t="shared" si="41"/>
+        <v>0.24174570649612137</v>
+      </c>
+      <c r="AP88" s="78">
+        <f t="shared" si="42"/>
+        <v>0.24333466449664484</v>
+      </c>
+    </row>
+    <row r="89" spans="1:42" x14ac:dyDescent="0.75">
+      <c r="A89" t="str">
+        <f t="shared" si="31"/>
+        <v>Deficit (Excl. Grants ) % of GDP</v>
+      </c>
+      <c r="AE89" s="144">
+        <v>-0.10715311961052623</v>
+      </c>
+      <c r="AF89" s="144">
+        <v>-0.13198602648404975</v>
+      </c>
+      <c r="AG89" s="144">
+        <v>-0.13819197250543944</v>
+      </c>
+      <c r="AH89" s="144">
+        <v>-0.1569715400252282</v>
+      </c>
+      <c r="AI89" s="144">
+        <v>-0.11571481494483828</v>
+      </c>
+      <c r="AJ89" s="144">
+        <v>-0.10810529497455036</v>
+      </c>
+      <c r="AK89" s="78">
+        <f t="shared" si="37"/>
+        <v>-8.3344978076517584E-2</v>
+      </c>
+      <c r="AL89" s="78">
+        <f t="shared" si="38"/>
+        <v>-8.4482142664593501E-2</v>
+      </c>
+      <c r="AM89" s="78">
+        <f t="shared" si="39"/>
+        <v>-7.0754572247162029E-2</v>
+      </c>
+      <c r="AN89" s="78">
+        <f t="shared" si="40"/>
+        <v>-6.6075913574943954E-2</v>
+      </c>
+      <c r="AO89" s="78">
+        <f t="shared" si="41"/>
+        <v>-5.1889440336449273E-2</v>
+      </c>
+      <c r="AP89" s="78">
+        <f t="shared" si="42"/>
+        <v>-5.0788531255510416E-2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.2" right="0.2" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup scale="49" orientation="landscape" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DD3143F-1CB5-4284-805F-149289AA16B5}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="53.6328125" customWidth="1"/>
     <col min="2" max="8" width="8.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A1" s="1"/>
-      <c r="B1" s="111">
+      <c r="B1" s="103">
         <v>2024</v>
       </c>
-      <c r="C1" s="111">
+      <c r="C1" s="103">
         <v>2025</v>
       </c>
-      <c r="D1" s="111">
+      <c r="D1" s="103">
         <v>2026</v>
       </c>
-      <c r="E1" s="111">
+      <c r="E1" s="103">
         <v>2027</v>
       </c>
-      <c r="F1" s="111">
+      <c r="F1" s="103">
         <v>2028</v>
       </c>
-      <c r="G1" s="111">
+      <c r="G1" s="103">
         <v>2029</v>
       </c>
-      <c r="H1" s="111">
+      <c r="H1" s="103">
         <v>2030</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A2" s="104" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A2" s="96" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="108">
+      <c r="C2" s="100">
         <f>C3+C4</f>
         <v>308.85861037162039</v>
       </c>
-      <c r="D2" s="108">
+      <c r="D2" s="100">
         <f t="shared" ref="D2:G2" si="0">D3+D4</f>
         <v>721.33994120659054</v>
       </c>
-      <c r="E2" s="108">
+      <c r="E2" s="100">
         <f t="shared" si="0"/>
         <v>732.21927019834698</v>
       </c>
-      <c r="F2" s="108">
+      <c r="F2" s="100">
         <f t="shared" si="0"/>
         <v>187.93653864476565</v>
       </c>
-      <c r="G2" s="108">
+      <c r="G2" s="100">
         <f t="shared" si="0"/>
         <v>4.2285111869296426</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A3" s="105" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A3" s="97" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="108">
+      <c r="C3" s="100">
         <v>174.00361037162037</v>
       </c>
-      <c r="D3" s="108">
+      <c r="D3" s="100">
         <v>385.4857976103541</v>
       </c>
-      <c r="E3" s="108">
+      <c r="E3" s="100">
         <v>439.33156211900854</v>
       </c>
-      <c r="F3" s="108">
+      <c r="F3" s="100">
         <v>112.76192318685943</v>
       </c>
-      <c r="G3" s="108">
+      <c r="G3" s="100">
         <v>2.5371067121577857</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A4" s="105" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A4" s="97" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="109">
+      <c r="C4" s="101">
         <v>134.85500000000002</v>
       </c>
-      <c r="D4" s="109">
+      <c r="D4" s="101">
         <v>335.85414359623644</v>
       </c>
-      <c r="E4" s="109">
+      <c r="E4" s="101">
         <v>292.88770807933849</v>
       </c>
-      <c r="F4" s="109">
+      <c r="F4" s="101">
         <v>75.174615457906214</v>
       </c>
-      <c r="G4" s="109">
+      <c r="G4" s="101">
         <v>1.6914044747718571</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A6" s="106" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A6" s="98" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="107">
+      <c r="B6" s="99">
         <v>1382.9873419999999</v>
       </c>
-      <c r="C6" s="107">
+      <c r="C6" s="99">
         <v>1455.0205468858974</v>
       </c>
-      <c r="D6" s="107">
+      <c r="D6" s="99">
         <v>1517.7698205635791</v>
       </c>
-      <c r="E6" s="107">
+      <c r="E6" s="99">
         <v>1572.0012687572651</v>
       </c>
-      <c r="F6" s="107">
+      <c r="F6" s="99">
         <v>1615.7148947336634</v>
       </c>
-      <c r="G6" s="107">
+      <c r="G6" s="99">
         <v>1656.1077671020048</v>
       </c>
-      <c r="H6" s="107">
+      <c r="H6" s="99">
         <v>1697.5104612795549</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="110">
+      <c r="C7" s="102">
         <f>C6/B6-1</f>
         <v>5.2085223557958971E-2</v>
       </c>
-      <c r="D7" s="110">
+      <c r="D7" s="102">
         <f t="shared" ref="D7:H7" si="1">D6/C6-1</f>
         <v>4.312603956829375E-2</v>
       </c>
-      <c r="E7" s="110">
+      <c r="E7" s="102">
         <f t="shared" si="1"/>
         <v>3.5731009708408035E-2</v>
       </c>
-      <c r="F7" s="110">
+      <c r="F7" s="102">
         <f t="shared" si="1"/>
         <v>2.7807627668746004E-2</v>
       </c>
-      <c r="G7" s="110">
+      <c r="G7" s="102">
         <f t="shared" si="1"/>
         <v>2.4999999999999911E-2</v>
       </c>
-      <c r="H7" s="110">
+      <c r="H7" s="102">
         <f t="shared" si="1"/>
         <v>2.4999999999999911E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107">
+      <c r="B8" s="99"/>
+      <c r="C8" s="99">
         <f>+(C6+B6)/2</f>
         <v>1419.0039444429485</v>
       </c>
-      <c r="D8" s="107">
+      <c r="D8" s="99">
         <f t="shared" ref="D8:H8" si="2">+(D6+C6)/2</f>
         <v>1486.3951837247382</v>
       </c>
-      <c r="E8" s="107">
+      <c r="E8" s="99">
         <f t="shared" si="2"/>
         <v>1544.8855446604221</v>
       </c>
-      <c r="F8" s="107">
+      <c r="F8" s="99">
         <f t="shared" si="2"/>
         <v>1593.8580817454642</v>
       </c>
-      <c r="G8" s="107">
+      <c r="G8" s="99">
         <f t="shared" si="2"/>
         <v>1635.9113309178342</v>
       </c>
-      <c r="H8" s="107">
+      <c r="H8" s="99">
         <f t="shared" si="2"/>
         <v>1676.8091141907798</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="C9" s="110"/>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="C9" s="102"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="C10" s="114">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="C10" s="106">
         <f>+C2*C8/1000</f>
         <v>438.27158639249711</v>
       </c>
-      <c r="D10" s="114">
+      <c r="D10" s="106">
         <f t="shared" ref="D10:G10" si="3">+D2*D8/1000</f>
         <v>1072.1962144377621</v>
       </c>
-      <c r="E10" s="114">
+      <c r="E10" s="106">
         <f t="shared" si="3"/>
         <v>1131.19496605123</v>
       </c>
-      <c r="F10" s="114">
+      <c r="F10" s="106">
         <f t="shared" si="3"/>
         <v>299.54417097422845</v>
       </c>
-      <c r="G10" s="114">
+      <c r="G10" s="106">
         <f t="shared" si="3"/>
         <v>6.9174693636110227</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A11" s="113" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A11" s="105" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="115">
+      <c r="C11" s="107">
         <f>+C3*C$8/1000</f>
         <v>246.91180946464326</v>
       </c>
-      <c r="D11" s="115">
+      <c r="D11" s="107">
         <f t="shared" ref="D11:G11" si="4">+D3*D$8/1000</f>
         <v>572.98423296231954</v>
       </c>
-      <c r="E11" s="115">
+      <c r="E11" s="107">
         <f t="shared" si="4"/>
         <v>678.71697963073848</v>
       </c>
-      <c r="F11" s="115">
+      <c r="F11" s="107">
         <f t="shared" si="4"/>
         <v>179.72650258453717</v>
       </c>
-      <c r="G11" s="115">
+      <c r="G11" s="107">
         <f t="shared" si="4"/>
         <v>4.150481618166614</v>
       </c>
-      <c r="H11" s="119">
+      <c r="H11" s="111">
         <f>SUM(C11:G11)</f>
         <v>1682.4900062604052</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A12" s="113" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A12" s="105" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="115">
+      <c r="C12" s="107">
         <f t="shared" ref="C12:G12" si="5">+C4*C$8/1000</f>
         <v>191.35977692785386</v>
       </c>
-      <c r="D12" s="115">
+      <c r="D12" s="107">
         <f t="shared" si="5"/>
         <v>499.21198147544249</v>
       </c>
-      <c r="E12" s="115">
+      <c r="E12" s="107">
         <f t="shared" si="5"/>
         <v>452.47798642049156</v>
       </c>
-      <c r="F12" s="115">
+      <c r="F12" s="107">
         <f t="shared" si="5"/>
         <v>119.81766838969132</v>
       </c>
-      <c r="G12" s="115">
+      <c r="G12" s="107">
         <f t="shared" si="5"/>
         <v>2.7669877454444092</v>
       </c>
-      <c r="H12" s="119">
+      <c r="H12" s="111">
         <f>SUM(C12:G12)</f>
         <v>1265.6344009589236</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="B16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="77">
+        <v>215.09287778667468</v>
+      </c>
+      <c r="D16" s="77">
+        <v>316.12001089561022</v>
+      </c>
+      <c r="E16" s="77">
+        <v>222.02911425810541</v>
+      </c>
+      <c r="F16" s="77">
+        <v>256.55184526664607</v>
+      </c>
+      <c r="G16" s="77">
+        <v>245.81139606098327</v>
+      </c>
+      <c r="H16" s="77">
+        <v>139.58835294766789</v>
+      </c>
+      <c r="I16" s="77">
+        <v>19.988717131596964</v>
+      </c>
+      <c r="J16" s="77">
+        <v>20.037246567619881</v>
+      </c>
+      <c r="K16" s="77">
+        <v>17.990922015319999</v>
+      </c>
+      <c r="L16" s="77">
+        <v>18.901575342420418</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="16" x14ac:dyDescent="0.8">
+      <c r="A17" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="23">
+        <f>C16-18</f>
+        <v>197.09287778667468</v>
+      </c>
+      <c r="D17" s="23">
+        <f t="shared" ref="D17:L17" si="6">D16-18</f>
+        <v>298.12001089561022</v>
+      </c>
+      <c r="E17" s="23">
+        <f t="shared" si="6"/>
+        <v>204.02911425810541</v>
+      </c>
+      <c r="F17" s="23">
+        <f t="shared" si="6"/>
+        <v>238.55184526664607</v>
+      </c>
+      <c r="G17" s="23">
+        <f t="shared" si="6"/>
+        <v>227.81139606098327</v>
+      </c>
+      <c r="H17" s="23">
+        <f t="shared" si="6"/>
+        <v>121.58835294766789</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="6"/>
+        <v>1.9887171315969638</v>
+      </c>
+      <c r="J17" s="23">
+        <f t="shared" si="6"/>
+        <v>2.0372465676198814</v>
+      </c>
+      <c r="K17" s="23">
+        <f t="shared" si="6"/>
+        <v>-9.0779846800010944E-3</v>
+      </c>
+      <c r="L17" s="23">
+        <f t="shared" si="6"/>
+        <v>0.90157534242041848</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="B19" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="14">
+        <f>D17+E17</f>
+        <v>502.14912515371566</v>
+      </c>
+      <c r="E19" s="14">
+        <f>F17+G17</f>
+        <v>466.36324132762934</v>
+      </c>
+      <c r="F19" s="14">
+        <f>G17+H17</f>
+        <v>349.39974900865116</v>
+      </c>
+      <c r="G19" s="14">
+        <f>I17+J17</f>
+        <v>4.0259636992168453</v>
+      </c>
+      <c r="H19" s="14">
+        <f>K17+L17</f>
+        <v>0.89249735774041739</v>
+      </c>
+      <c r="I19" s="145">
+        <f>SUM(D19:H19)</f>
+        <v>1322.8305765469536</v>
       </c>
     </row>
   </sheetData>
